--- a/research/traditional_assets/database/data/mauritius/mauritius_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_hospitals_healthcare_facilities.xlsx
@@ -1133,7 +1133,7 @@
         <v>3.85957446808511</v>
       </c>
       <c r="F2">
-        <v>4.62198709344291</v>
+        <v>4.6219870934429</v>
       </c>
       <c r="G2">
         <v>2.80272108843537</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0868357761082095</v>
+        <v>0.08674377244404718</v>
       </c>
       <c r="C2">
-        <v>157.9782443514634</v>
+        <v>156.8885634427531</v>
       </c>
       <c r="D2">
-        <v>157.6802443514634</v>
+        <v>158.0345634427531</v>
       </c>
       <c r="E2">
-        <v>-41.2</v>
+        <v>-39.756</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.444</v>
       </c>
       <c r="G2">
         <v>0.298</v>
@@ -1451,28 +1451,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.07263320000000001</v>
       </c>
       <c r="N2">
-        <v>10.70333333333333</v>
+        <v>10.63070013333333</v>
       </c>
       <c r="O2">
-        <v>1.6055</v>
+        <v>1.59460502</v>
       </c>
       <c r="P2">
-        <v>9.097833333333334</v>
+        <v>9.036095113333333</v>
       </c>
       <c r="Q2">
-        <v>14.72783333333333</v>
+        <v>14.66609511333333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0868357761082095</v>
+        <v>0.08718810347883554</v>
       </c>
       <c r="T2">
-        <v>0.5648729042001043</v>
+        <v>0.5697228230745496</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>147.3614453629102</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08674377244404718</v>
+        <v>0.08665176877988488</v>
       </c>
       <c r="C3">
-        <v>156.8885634427531</v>
+        <v>155.8004784823041</v>
       </c>
       <c r="D3">
-        <v>158.0345634427531</v>
+        <v>158.3904784823041</v>
       </c>
       <c r="E3">
-        <v>-39.756</v>
+        <v>-38.312</v>
       </c>
       <c r="F3">
-        <v>1.444</v>
+        <v>2.888</v>
       </c>
       <c r="G3">
         <v>0.298</v>
@@ -1533,28 +1533,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M3">
-        <v>0.07263320000000001</v>
+        <v>0.1452664</v>
       </c>
       <c r="N3">
-        <v>10.63070013333333</v>
+        <v>10.55806693333333</v>
       </c>
       <c r="O3">
-        <v>1.59460502</v>
+        <v>1.58371004</v>
       </c>
       <c r="P3">
-        <v>9.036095113333333</v>
+        <v>8.974356893333333</v>
       </c>
       <c r="Q3">
-        <v>14.66609511333333</v>
+        <v>14.60435689333333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08718810347883554</v>
+        <v>0.08754762120396417</v>
       </c>
       <c r="T3">
-        <v>0.5697228230745496</v>
+        <v>0.5746717198852082</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>147.3614453629102</v>
+        <v>73.68072268145511</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08665176877988488</v>
+        <v>0.08655976511572257</v>
       </c>
       <c r="C4">
-        <v>155.8004784823041</v>
+        <v>154.7140002773248</v>
       </c>
       <c r="D4">
-        <v>158.3904784823041</v>
+        <v>158.7480002773248</v>
       </c>
       <c r="E4">
-        <v>-38.312</v>
+        <v>-36.868</v>
       </c>
       <c r="F4">
-        <v>2.888</v>
+        <v>4.332</v>
       </c>
       <c r="G4">
         <v>0.298</v>
@@ -1615,28 +1615,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M4">
-        <v>0.1452664</v>
+        <v>0.2178996</v>
       </c>
       <c r="N4">
-        <v>10.55806693333333</v>
+        <v>10.48543373333333</v>
       </c>
       <c r="O4">
-        <v>1.58371004</v>
+        <v>1.57281506</v>
       </c>
       <c r="P4">
-        <v>8.974356893333333</v>
+        <v>8.912618673333334</v>
       </c>
       <c r="Q4">
-        <v>14.60435689333333</v>
+        <v>14.54261867333333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08754762120396417</v>
+        <v>0.08791455166569337</v>
       </c>
       <c r="T4">
-        <v>0.5746717198852082</v>
+        <v>0.5797226558053648</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.68072268145511</v>
+        <v>49.12048178763676</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08655976511572257</v>
+        <v>0.08646776145156025</v>
       </c>
       <c r="C5">
-        <v>154.7140002773248</v>
+        <v>153.6291397328208</v>
       </c>
       <c r="D5">
-        <v>158.7480002773248</v>
+        <v>159.1071397328208</v>
       </c>
       <c r="E5">
-        <v>-36.868</v>
+        <v>-35.424</v>
       </c>
       <c r="F5">
-        <v>4.332</v>
+        <v>5.776000000000001</v>
       </c>
       <c r="G5">
         <v>0.298</v>
@@ -1697,28 +1697,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M5">
-        <v>0.2178996</v>
+        <v>0.2905328</v>
       </c>
       <c r="N5">
-        <v>10.48543373333333</v>
+        <v>10.41280053333333</v>
       </c>
       <c r="O5">
-        <v>1.57281506</v>
+        <v>1.56192008</v>
       </c>
       <c r="P5">
-        <v>8.912618673333334</v>
+        <v>8.850880453333334</v>
       </c>
       <c r="Q5">
-        <v>14.54261867333333</v>
+        <v>14.48088045333333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08791455166569337</v>
+        <v>0.08828912651204193</v>
       </c>
       <c r="T5">
-        <v>0.5797226558053648</v>
+        <v>0.5848788195571913</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>49.12048178763676</v>
+        <v>36.84036134072756</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08646776145156025</v>
+        <v>0.08637575778739792</v>
       </c>
       <c r="C6">
-        <v>153.6291397328208</v>
+        <v>152.5459078527043</v>
       </c>
       <c r="D6">
-        <v>159.1071397328208</v>
+        <v>159.4679078527043</v>
       </c>
       <c r="E6">
-        <v>-35.424</v>
+        <v>-33.98</v>
       </c>
       <c r="F6">
-        <v>5.776000000000001</v>
+        <v>7.220000000000001</v>
       </c>
       <c r="G6">
         <v>0.298</v>
@@ -1779,28 +1779,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M6">
-        <v>0.2905328</v>
+        <v>0.363166</v>
       </c>
       <c r="N6">
-        <v>10.41280053333333</v>
+        <v>10.34016733333333</v>
       </c>
       <c r="O6">
-        <v>1.56192008</v>
+        <v>1.5510251</v>
       </c>
       <c r="P6">
-        <v>8.850880453333334</v>
+        <v>8.789142233333333</v>
       </c>
       <c r="Q6">
-        <v>14.48088045333333</v>
+        <v>14.41914223333333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08828912651204193</v>
+        <v>0.0886715871446294</v>
       </c>
       <c r="T6">
-        <v>0.5848788195571913</v>
+        <v>0.5901435341248458</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.84036134072756</v>
+        <v>29.47228907258205</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08637575778739792</v>
+        <v>0.08628375412323562</v>
       </c>
       <c r="C7">
-        <v>152.5459078527043</v>
+        <v>151.4643157409175</v>
       </c>
       <c r="D7">
-        <v>159.4679078527043</v>
+        <v>159.8303157409175</v>
       </c>
       <c r="E7">
-        <v>-33.98</v>
+        <v>-32.536</v>
       </c>
       <c r="F7">
-        <v>7.220000000000001</v>
+        <v>8.664000000000001</v>
       </c>
       <c r="G7">
         <v>0.298</v>
@@ -1861,28 +1861,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M7">
-        <v>0.363166</v>
+        <v>0.4357992000000001</v>
       </c>
       <c r="N7">
-        <v>10.34016733333333</v>
+        <v>10.26753413333333</v>
       </c>
       <c r="O7">
-        <v>1.5510251</v>
+        <v>1.54013012</v>
       </c>
       <c r="P7">
-        <v>8.789142233333333</v>
+        <v>8.727404013333333</v>
       </c>
       <c r="Q7">
-        <v>14.41914223333333</v>
+        <v>14.35740401333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0886715871446294</v>
+        <v>0.0890621852374847</v>
       </c>
       <c r="T7">
-        <v>0.5901435341248458</v>
+        <v>0.5955202638960674</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.47228907258205</v>
+        <v>24.56024089381837</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08628375412323561</v>
+        <v>0.08619175045907332</v>
       </c>
       <c r="C8">
-        <v>151.4643157409176</v>
+        <v>150.3843746025724</v>
       </c>
       <c r="D8">
-        <v>159.8303157409175</v>
+        <v>160.1943746025725</v>
       </c>
       <c r="E8">
-        <v>-32.536</v>
+        <v>-31.09200000000001</v>
       </c>
       <c r="F8">
-        <v>8.664</v>
+        <v>10.108</v>
       </c>
       <c r="G8">
         <v>0.298</v>
@@ -1943,28 +1943,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M8">
-        <v>0.4357991999999999</v>
+        <v>0.5084323999999999</v>
       </c>
       <c r="N8">
-        <v>10.26753413333333</v>
+        <v>10.19490093333333</v>
       </c>
       <c r="O8">
-        <v>1.54013012</v>
+        <v>1.52923514</v>
       </c>
       <c r="P8">
-        <v>8.727404013333333</v>
+        <v>8.665665793333332</v>
       </c>
       <c r="Q8">
-        <v>14.35740401333333</v>
+        <v>14.29566579333333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0890621852374847</v>
+        <v>0.08946118328932613</v>
       </c>
       <c r="T8">
-        <v>0.5955202638960674</v>
+        <v>0.6010126222645196</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.56024089381838</v>
+        <v>21.05163505184433</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0861917504590733</v>
+        <v>0.086099746794911</v>
       </c>
       <c r="C9">
-        <v>150.3843746025725</v>
+        <v>149.3060957451055</v>
       </c>
       <c r="D9">
-        <v>160.1943746025725</v>
+        <v>160.5600957451055</v>
       </c>
       <c r="E9">
-        <v>-31.092</v>
+        <v>-29.648</v>
       </c>
       <c r="F9">
-        <v>10.108</v>
+        <v>11.552</v>
       </c>
       <c r="G9">
         <v>0.298</v>
@@ -2025,28 +2025,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M9">
-        <v>0.5084324</v>
+        <v>0.5810656000000001</v>
       </c>
       <c r="N9">
-        <v>10.19490093333333</v>
+        <v>10.12226773333333</v>
       </c>
       <c r="O9">
-        <v>1.52923514</v>
+        <v>1.51834016</v>
       </c>
       <c r="P9">
-        <v>8.665665793333332</v>
+        <v>8.603927573333333</v>
       </c>
       <c r="Q9">
-        <v>14.29566579333333</v>
+        <v>14.23392757333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08946118328932613</v>
+        <v>0.08986885521185978</v>
       </c>
       <c r="T9">
-        <v>0.6010126222645196</v>
+        <v>0.606624379727938</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.05163505184432</v>
+        <v>18.42018067036378</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.086099746794911</v>
+        <v>0.08600774313074867</v>
       </c>
       <c r="C10">
-        <v>149.3060957451055</v>
+        <v>148.2294905794479</v>
       </c>
       <c r="D10">
-        <v>160.5600957451055</v>
+        <v>160.9274905794479</v>
       </c>
       <c r="E10">
-        <v>-29.648</v>
+        <v>-28.204</v>
       </c>
       <c r="F10">
-        <v>11.552</v>
+        <v>12.996</v>
       </c>
       <c r="G10">
         <v>0.298</v>
@@ -2107,28 +2107,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M10">
-        <v>0.5810656000000001</v>
+        <v>0.6536988</v>
       </c>
       <c r="N10">
-        <v>10.12226773333333</v>
+        <v>10.04963453333333</v>
       </c>
       <c r="O10">
-        <v>1.51834016</v>
+        <v>1.50744518</v>
       </c>
       <c r="P10">
-        <v>8.603927573333333</v>
+        <v>8.542189353333333</v>
       </c>
       <c r="Q10">
-        <v>14.23392757333333</v>
+        <v>14.17218935333333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08986885521185978</v>
+        <v>0.09028548695686667</v>
       </c>
       <c r="T10">
-        <v>0.606624379727938</v>
+        <v>0.6123594725202229</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.42018067036378</v>
+        <v>16.37349392921225</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08600774313074867</v>
+        <v>0.08591573946658637</v>
       </c>
       <c r="C11">
-        <v>148.2294905794479</v>
+        <v>147.1545706212127</v>
       </c>
       <c r="D11">
-        <v>160.9274905794479</v>
+        <v>161.2965706212127</v>
       </c>
       <c r="E11">
-        <v>-28.204</v>
+        <v>-26.76000000000001</v>
       </c>
       <c r="F11">
-        <v>12.996</v>
+        <v>14.44</v>
       </c>
       <c r="G11">
         <v>0.298</v>
@@ -2189,28 +2189,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M11">
-        <v>0.6536988</v>
+        <v>0.726332</v>
       </c>
       <c r="N11">
-        <v>10.04963453333333</v>
+        <v>9.977001333333334</v>
       </c>
       <c r="O11">
-        <v>1.50744518</v>
+        <v>1.4965502</v>
       </c>
       <c r="P11">
-        <v>8.542189353333333</v>
+        <v>8.480451133333334</v>
       </c>
       <c r="Q11">
-        <v>14.17218935333333</v>
+        <v>14.11045113333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09028548695686667</v>
+        <v>0.09071137718509596</v>
       </c>
       <c r="T11">
-        <v>0.6123594725202229</v>
+        <v>0.618222011819003</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.37349392921225</v>
+        <v>14.73614453629103</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08591573946658637</v>
+        <v>0.08582373580242406</v>
       </c>
       <c r="C12">
-        <v>147.1545706212127</v>
+        <v>146.0813474918983</v>
       </c>
       <c r="D12">
-        <v>161.2965706212127</v>
+        <v>161.6673474918983</v>
       </c>
       <c r="E12">
-        <v>-26.76</v>
+        <v>-25.316</v>
       </c>
       <c r="F12">
-        <v>14.44</v>
+        <v>15.884</v>
       </c>
       <c r="G12">
         <v>0.298</v>
@@ -2271,28 +2271,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M12">
-        <v>0.726332</v>
+        <v>0.7989651999999999</v>
       </c>
       <c r="N12">
-        <v>9.977001333333334</v>
+        <v>9.904368133333334</v>
       </c>
       <c r="O12">
-        <v>1.4965502</v>
+        <v>1.48565522</v>
       </c>
       <c r="P12">
-        <v>8.480451133333334</v>
+        <v>8.418712913333334</v>
       </c>
       <c r="Q12">
-        <v>14.11045113333333</v>
+        <v>14.04871291333333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09071137718509596</v>
+        <v>0.09114683798025175</v>
       </c>
       <c r="T12">
-        <v>0.618222011819003</v>
+        <v>0.6242162935739355</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.73614453629103</v>
+        <v>13.39649503299184</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08582373580242406</v>
+        <v>0.08588473213826174</v>
       </c>
       <c r="C13">
-        <v>146.0813474918983</v>
+        <v>144.3913407133675</v>
       </c>
       <c r="D13">
-        <v>161.6673474918983</v>
+        <v>161.4213407133675</v>
       </c>
       <c r="E13">
-        <v>-25.316</v>
+        <v>-23.872</v>
       </c>
       <c r="F13">
-        <v>15.884</v>
+        <v>17.328</v>
       </c>
       <c r="G13">
         <v>0.298</v>
@@ -2353,45 +2353,45 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M13">
-        <v>0.7989651999999999</v>
+        <v>0.8975903999999999</v>
       </c>
       <c r="N13">
-        <v>9.904368133333334</v>
+        <v>9.805742933333333</v>
       </c>
       <c r="O13">
-        <v>1.48565522</v>
+        <v>1.47086144</v>
       </c>
       <c r="P13">
-        <v>8.418712913333334</v>
+        <v>8.334881493333333</v>
       </c>
       <c r="Q13">
-        <v>14.04871291333333</v>
+        <v>13.96488149333333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09114683798025175</v>
+        <v>0.09159219561166107</v>
       </c>
       <c r="T13">
-        <v>0.6242162935739355</v>
+        <v>0.6303468090051164</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.15</v>
       </c>
       <c r="W13">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.39649503299184</v>
+        <v>11.92451850346587</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08588473213826174</v>
+        <v>0.08580547847409942</v>
       </c>
       <c r="C14">
-        <v>144.3913407133675</v>
+        <v>143.2671277328831</v>
       </c>
       <c r="D14">
-        <v>161.4213407133675</v>
+        <v>161.7411277328831</v>
       </c>
       <c r="E14">
-        <v>-23.872</v>
+        <v>-22.428</v>
       </c>
       <c r="F14">
-        <v>17.328</v>
+        <v>18.772</v>
       </c>
       <c r="G14">
         <v>0.298</v>
@@ -2435,28 +2435,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M14">
-        <v>0.8975903999999999</v>
+        <v>0.9723896000000001</v>
       </c>
       <c r="N14">
-        <v>9.805742933333333</v>
+        <v>9.730943733333334</v>
       </c>
       <c r="O14">
-        <v>1.47086144</v>
+        <v>1.45964156</v>
       </c>
       <c r="P14">
-        <v>8.334881493333333</v>
+        <v>8.271302173333334</v>
       </c>
       <c r="Q14">
-        <v>13.96488149333333</v>
+        <v>13.90130217333333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09159219561166107</v>
+        <v>0.09204779134953955</v>
       </c>
       <c r="T14">
-        <v>0.6303468090051164</v>
+        <v>0.6366182558255198</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.92451850346587</v>
+        <v>11.00724784935311</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08580547847409942</v>
+        <v>0.08572622480993709</v>
       </c>
       <c r="C15">
-        <v>143.2671277328831</v>
+        <v>142.1441843085949</v>
       </c>
       <c r="D15">
-        <v>161.7411277328831</v>
+        <v>162.0621843085949</v>
       </c>
       <c r="E15">
-        <v>-22.428</v>
+        <v>-20.984</v>
       </c>
       <c r="F15">
-        <v>18.772</v>
+        <v>20.216</v>
       </c>
       <c r="G15">
         <v>0.298</v>
@@ -2517,28 +2517,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M15">
-        <v>0.9723896000000001</v>
+        <v>1.0471888</v>
       </c>
       <c r="N15">
-        <v>9.730943733333334</v>
+        <v>9.656144533333332</v>
       </c>
       <c r="O15">
-        <v>1.45964156</v>
+        <v>1.44842168</v>
       </c>
       <c r="P15">
-        <v>8.271302173333334</v>
+        <v>8.207722853333333</v>
       </c>
       <c r="Q15">
-        <v>13.90130217333333</v>
+        <v>13.83772285333333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09204779134953955</v>
+        <v>0.09251398233713616</v>
       </c>
       <c r="T15">
-        <v>0.6366182558255198</v>
+        <v>0.6430355502463977</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.00724784935311</v>
+        <v>10.2210158601136</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08572622480993709</v>
+        <v>0.08586372114577479</v>
       </c>
       <c r="C16">
-        <v>142.1441843085949</v>
+        <v>140.1439964188278</v>
       </c>
       <c r="D16">
-        <v>162.0621843085949</v>
+        <v>161.5059964188278</v>
       </c>
       <c r="E16">
-        <v>-20.984</v>
+        <v>-19.54</v>
       </c>
       <c r="F16">
-        <v>20.216</v>
+        <v>21.66</v>
       </c>
       <c r="G16">
         <v>0.298</v>
@@ -2599,45 +2599,45 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M16">
-        <v>1.0471888</v>
+        <v>1.15881</v>
       </c>
       <c r="N16">
-        <v>9.656144533333332</v>
+        <v>9.544523333333332</v>
       </c>
       <c r="O16">
-        <v>1.44842168</v>
+        <v>1.4316785</v>
       </c>
       <c r="P16">
-        <v>8.207722853333333</v>
+        <v>8.112844833333332</v>
       </c>
       <c r="Q16">
-        <v>13.83772285333333</v>
+        <v>13.74284483333333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09251398233713616</v>
+        <v>0.09299114252444092</v>
       </c>
       <c r="T16">
-        <v>0.6430355502463977</v>
+        <v>0.6496038398301198</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.15</v>
       </c>
       <c r="W16">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.2210158601136</v>
+        <v>9.236486855768703</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08586372114577479</v>
+        <v>0.08579891748161249</v>
       </c>
       <c r="C17">
-        <v>140.1439964188278</v>
+        <v>138.961658008968</v>
       </c>
       <c r="D17">
-        <v>161.5059964188278</v>
+        <v>161.767658008968</v>
       </c>
       <c r="E17">
-        <v>-19.54</v>
+        <v>-18.096</v>
       </c>
       <c r="F17">
-        <v>21.66</v>
+        <v>23.104</v>
       </c>
       <c r="G17">
         <v>0.298</v>
@@ -2681,28 +2681,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M17">
-        <v>1.15881</v>
+        <v>1.236064</v>
       </c>
       <c r="N17">
-        <v>9.544523333333334</v>
+        <v>9.467269333333332</v>
       </c>
       <c r="O17">
-        <v>1.4316785</v>
+        <v>1.4200904</v>
       </c>
       <c r="P17">
-        <v>8.112844833333334</v>
+        <v>8.047178933333333</v>
       </c>
       <c r="Q17">
-        <v>13.74284483333333</v>
+        <v>13.67717893333333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09299114252444092</v>
+        <v>0.09347966366858629</v>
       </c>
       <c r="T17">
-        <v>0.6496038398301198</v>
+        <v>0.6563285172610736</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.236486855768707</v>
+        <v>8.659206427283159</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08579891748161249</v>
+        <v>0.08573411381745015</v>
       </c>
       <c r="C18">
-        <v>138.961658008968</v>
+        <v>137.7801688294124</v>
       </c>
       <c r="D18">
-        <v>161.767658008968</v>
+        <v>162.0301688294124</v>
       </c>
       <c r="E18">
-        <v>-18.096</v>
+        <v>-16.652</v>
       </c>
       <c r="F18">
-        <v>23.104</v>
+        <v>24.548</v>
       </c>
       <c r="G18">
         <v>0.298</v>
@@ -2763,28 +2763,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M18">
-        <v>1.236064</v>
+        <v>1.313318</v>
       </c>
       <c r="N18">
-        <v>9.467269333333332</v>
+        <v>9.390015333333332</v>
       </c>
       <c r="O18">
-        <v>1.4200904</v>
+        <v>1.4085023</v>
       </c>
       <c r="P18">
-        <v>8.047178933333333</v>
+        <v>7.981513033333332</v>
       </c>
       <c r="Q18">
-        <v>13.67717893333333</v>
+        <v>13.61151303333333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09347966366858629</v>
+        <v>0.09397995640656646</v>
       </c>
       <c r="T18">
-        <v>0.6563285172610736</v>
+        <v>0.6632152351120502</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.659206427283159</v>
+        <v>8.149841343325328</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08573411381745015</v>
+        <v>0.08566931015328785</v>
       </c>
       <c r="C19">
-        <v>137.7801688294124</v>
+        <v>136.5995330211833</v>
       </c>
       <c r="D19">
-        <v>162.0301688294124</v>
+        <v>162.2935330211833</v>
       </c>
       <c r="E19">
-        <v>-16.652</v>
+        <v>-15.208</v>
       </c>
       <c r="F19">
-        <v>24.548</v>
+        <v>25.992</v>
       </c>
       <c r="G19">
         <v>0.298</v>
@@ -2845,28 +2845,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M19">
-        <v>1.313318</v>
+        <v>1.390572</v>
       </c>
       <c r="N19">
-        <v>9.390015333333332</v>
+        <v>9.312761333333333</v>
       </c>
       <c r="O19">
-        <v>1.4085023</v>
+        <v>1.3969142</v>
       </c>
       <c r="P19">
-        <v>7.981513033333332</v>
+        <v>7.915847133333333</v>
       </c>
       <c r="Q19">
-        <v>13.61151303333333</v>
+        <v>13.54584713333333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09397995640656646</v>
+        <v>0.0944924514064486</v>
       </c>
       <c r="T19">
-        <v>0.6632152351120502</v>
+        <v>0.6702699216910993</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.149841343325328</v>
+        <v>7.697072379807254</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08566931015328785</v>
+        <v>0.08573370648912554</v>
       </c>
       <c r="C20">
-        <v>136.5995330211833</v>
+        <v>134.8938215554679</v>
       </c>
       <c r="D20">
-        <v>162.2935330211833</v>
+        <v>162.0318215554679</v>
       </c>
       <c r="E20">
-        <v>-15.208</v>
+        <v>-13.764</v>
       </c>
       <c r="F20">
-        <v>25.992</v>
+        <v>27.436</v>
       </c>
       <c r="G20">
         <v>0.298</v>
@@ -2927,45 +2927,45 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M20">
-        <v>1.390572</v>
+        <v>1.4897748</v>
       </c>
       <c r="N20">
-        <v>9.312761333333333</v>
+        <v>9.213558533333334</v>
       </c>
       <c r="O20">
-        <v>1.3969142</v>
+        <v>1.38203378</v>
       </c>
       <c r="P20">
-        <v>7.915847133333333</v>
+        <v>7.831524753333333</v>
       </c>
       <c r="Q20">
-        <v>13.54584713333333</v>
+        <v>13.46152475333333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0944924514064486</v>
+        <v>0.09501760060385868</v>
       </c>
       <c r="T20">
-        <v>0.6702699216910993</v>
+        <v>0.6774987980622238</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.697072379807254</v>
+        <v>7.184531066932623</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08573370648912554</v>
+        <v>0.08567570282496322</v>
       </c>
       <c r="C21">
-        <v>134.8938215554679</v>
+        <v>133.6855149400427</v>
       </c>
       <c r="D21">
-        <v>162.0318215554679</v>
+        <v>162.2675149400426</v>
       </c>
       <c r="E21">
-        <v>-13.764</v>
+        <v>-12.32</v>
       </c>
       <c r="F21">
-        <v>27.436</v>
+        <v>28.88</v>
       </c>
       <c r="G21">
         <v>0.298</v>
@@ -3009,28 +3009,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M21">
-        <v>1.4897748</v>
+        <v>1.568184</v>
       </c>
       <c r="N21">
-        <v>9.213558533333334</v>
+        <v>9.135149333333333</v>
       </c>
       <c r="O21">
-        <v>1.38203378</v>
+        <v>1.3702724</v>
       </c>
       <c r="P21">
-        <v>7.831524753333333</v>
+        <v>7.764876933333333</v>
       </c>
       <c r="Q21">
-        <v>13.46152475333333</v>
+        <v>13.39487693333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09501760060385868</v>
+        <v>0.09555587853120401</v>
       </c>
       <c r="T21">
-        <v>0.6774987980622238</v>
+        <v>0.6849083963426263</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.184531066932623</v>
+        <v>6.82530451358599</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08567570282496322</v>
+        <v>0.08561769916080092</v>
       </c>
       <c r="C22">
-        <v>133.6855149400427</v>
+        <v>132.4778950081883</v>
       </c>
       <c r="D22">
-        <v>162.2675149400426</v>
+        <v>162.5038950081883</v>
       </c>
       <c r="E22">
-        <v>-12.32</v>
+        <v>-10.876</v>
       </c>
       <c r="F22">
-        <v>28.88</v>
+        <v>30.32400000000001</v>
       </c>
       <c r="G22">
         <v>0.298</v>
@@ -3091,28 +3091,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M22">
-        <v>1.568184</v>
+        <v>1.6465932</v>
       </c>
       <c r="N22">
-        <v>9.135149333333333</v>
+        <v>9.056740133333333</v>
       </c>
       <c r="O22">
-        <v>1.3702724</v>
+        <v>1.35851102</v>
       </c>
       <c r="P22">
-        <v>7.764876933333333</v>
+        <v>7.698229113333333</v>
       </c>
       <c r="Q22">
-        <v>13.39487693333333</v>
+        <v>13.32822911333333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09555587853120401</v>
+        <v>0.09610778374784926</v>
       </c>
       <c r="T22">
-        <v>0.6849083963426263</v>
+        <v>0.6925055793896215</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.82530451358599</v>
+        <v>6.500290012939038</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08561769916080091</v>
+        <v>0.08555969549663858</v>
       </c>
       <c r="C23">
-        <v>132.4778950081883</v>
+        <v>131.2709647652221</v>
       </c>
       <c r="D23">
-        <v>162.5038950081883</v>
+        <v>162.7409647652221</v>
       </c>
       <c r="E23">
-        <v>-10.876</v>
+        <v>-9.432000000000002</v>
       </c>
       <c r="F23">
-        <v>30.324</v>
+        <v>31.768</v>
       </c>
       <c r="G23">
         <v>0.298</v>
@@ -3173,28 +3173,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M23">
-        <v>1.6465932</v>
+        <v>1.7250024</v>
       </c>
       <c r="N23">
-        <v>9.056740133333333</v>
+        <v>8.978330933333332</v>
       </c>
       <c r="O23">
-        <v>1.35851102</v>
+        <v>1.34674964</v>
       </c>
       <c r="P23">
-        <v>7.698229113333333</v>
+        <v>7.631581293333332</v>
       </c>
       <c r="Q23">
-        <v>13.32822911333333</v>
+        <v>13.26158129333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09610778374784924</v>
+        <v>0.09667384038030588</v>
       </c>
       <c r="T23">
-        <v>0.6925055793896214</v>
+        <v>0.7002975620019242</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.500290012939039</v>
+        <v>6.204822285078172</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08555969549663858</v>
+        <v>0.08569719183247629</v>
       </c>
       <c r="C24">
-        <v>131.2709647652221</v>
+        <v>129.2661161110144</v>
       </c>
       <c r="D24">
-        <v>162.7409647652221</v>
+        <v>162.1801161110144</v>
       </c>
       <c r="E24">
-        <v>-9.432000000000002</v>
+        <v>-7.988</v>
       </c>
       <c r="F24">
-        <v>31.768</v>
+        <v>33.212</v>
       </c>
       <c r="G24">
         <v>0.298</v>
@@ -3255,45 +3255,45 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M24">
-        <v>1.7250024</v>
+        <v>1.8366236</v>
       </c>
       <c r="N24">
-        <v>8.978330933333332</v>
+        <v>8.866709733333334</v>
       </c>
       <c r="O24">
-        <v>1.34674964</v>
+        <v>1.33000646</v>
       </c>
       <c r="P24">
-        <v>7.631581293333332</v>
+        <v>7.536703273333334</v>
       </c>
       <c r="Q24">
-        <v>13.26158129333333</v>
+        <v>13.16670327333333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09667384038030588</v>
+        <v>0.09725459978243672</v>
       </c>
       <c r="T24">
-        <v>0.7002975620019242</v>
+        <v>0.7082919337729878</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.15</v>
       </c>
       <c r="W24">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.204822285078172</v>
+        <v>5.827722856949749</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08569719183247629</v>
+        <v>0.08564768816831396</v>
       </c>
       <c r="C25">
-        <v>129.2661161110144</v>
+        <v>128.0235960555435</v>
       </c>
       <c r="D25">
-        <v>162.1801161110144</v>
+        <v>162.3815960555436</v>
       </c>
       <c r="E25">
-        <v>-7.988</v>
+        <v>-6.543999999999997</v>
       </c>
       <c r="F25">
-        <v>33.212</v>
+        <v>34.65600000000001</v>
       </c>
       <c r="G25">
         <v>0.298</v>
@@ -3337,28 +3337,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M25">
-        <v>1.8366236</v>
+        <v>1.9164768</v>
       </c>
       <c r="N25">
-        <v>8.866709733333334</v>
+        <v>8.786856533333333</v>
       </c>
       <c r="O25">
-        <v>1.33000646</v>
+        <v>1.31802848</v>
       </c>
       <c r="P25">
-        <v>7.536703273333334</v>
+        <v>7.468828053333334</v>
       </c>
       <c r="Q25">
-        <v>13.16670327333333</v>
+        <v>13.09882805333333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09725459978243672</v>
+        <v>0.09785064232672888</v>
       </c>
       <c r="T25">
-        <v>0.7082919337729878</v>
+        <v>0.7164966837485532</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.827722856949749</v>
+        <v>5.584901071243509</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08564768816831396</v>
+        <v>0.08559818450415164</v>
       </c>
       <c r="C26">
-        <v>128.0235960555435</v>
+        <v>126.7815772287409</v>
       </c>
       <c r="D26">
-        <v>162.3815960555436</v>
+        <v>162.5835772287409</v>
       </c>
       <c r="E26">
-        <v>-6.544000000000004</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="F26">
-        <v>34.656</v>
+        <v>36.1</v>
       </c>
       <c r="G26">
         <v>0.298</v>
@@ -3419,28 +3419,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M26">
-        <v>1.9164768</v>
+        <v>1.99633</v>
       </c>
       <c r="N26">
-        <v>8.786856533333333</v>
+        <v>8.707003333333333</v>
       </c>
       <c r="O26">
-        <v>1.31802848</v>
+        <v>1.3060505</v>
       </c>
       <c r="P26">
-        <v>7.468828053333334</v>
+        <v>7.400952833333333</v>
       </c>
       <c r="Q26">
-        <v>13.09882805333333</v>
+        <v>13.03095283333333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09785064232672888</v>
+        <v>0.09846257933886886</v>
       </c>
       <c r="T26">
-        <v>0.7164966837485532</v>
+        <v>0.7249202270568004</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.584901071243509</v>
+        <v>5.361505028393768</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08559818450415164</v>
+        <v>0.08554868083998933</v>
       </c>
       <c r="C27">
-        <v>126.7815772287409</v>
+        <v>125.540061503322</v>
       </c>
       <c r="D27">
-        <v>162.5835772287409</v>
+        <v>162.786061503322</v>
       </c>
       <c r="E27">
-        <v>-5.100000000000001</v>
+        <v>-3.655999999999999</v>
       </c>
       <c r="F27">
-        <v>36.1</v>
+        <v>37.544</v>
       </c>
       <c r="G27">
         <v>0.298</v>
@@ -3501,28 +3501,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M27">
-        <v>1.99633</v>
+        <v>2.0761832</v>
       </c>
       <c r="N27">
-        <v>8.707003333333333</v>
+        <v>8.627150133333332</v>
       </c>
       <c r="O27">
-        <v>1.3060505</v>
+        <v>1.29407252</v>
       </c>
       <c r="P27">
-        <v>7.400952833333333</v>
+        <v>7.333077613333332</v>
       </c>
       <c r="Q27">
-        <v>13.03095283333333</v>
+        <v>12.96307761333333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09846257933886886</v>
+        <v>0.09909105518917477</v>
       </c>
       <c r="T27">
-        <v>0.7249202270568004</v>
+        <v>0.7335714336977029</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.361505028393768</v>
+        <v>5.155293296532469</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08554868083998933</v>
+        <v>0.08549917717582703</v>
       </c>
       <c r="C28">
-        <v>125.540061503322</v>
+        <v>124.299050761343</v>
       </c>
       <c r="D28">
-        <v>162.786061503322</v>
+        <v>162.989050761343</v>
       </c>
       <c r="E28">
-        <v>-3.655999999999999</v>
+        <v>-2.211999999999996</v>
       </c>
       <c r="F28">
-        <v>37.544</v>
+        <v>38.98800000000001</v>
       </c>
       <c r="G28">
         <v>0.298</v>
@@ -3583,28 +3583,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M28">
-        <v>2.0761832</v>
+        <v>2.156036400000001</v>
       </c>
       <c r="N28">
-        <v>8.627150133333332</v>
+        <v>8.547296933333332</v>
       </c>
       <c r="O28">
-        <v>1.29407252</v>
+        <v>1.28209454</v>
       </c>
       <c r="P28">
-        <v>7.333077613333332</v>
+        <v>7.265202393333333</v>
       </c>
       <c r="Q28">
-        <v>12.96307761333333</v>
+        <v>12.89520239333333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09909105518917477</v>
+        <v>0.09973674955592743</v>
       </c>
       <c r="T28">
-        <v>0.7335714336977029</v>
+        <v>0.7424596596986303</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.155293296532469</v>
+        <v>4.964356507772006</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08549917717582703</v>
+        <v>0.08544967351166471</v>
       </c>
       <c r="C29">
-        <v>124.299050761343</v>
+        <v>123.0585468942594</v>
       </c>
       <c r="D29">
-        <v>162.989050761343</v>
+        <v>163.1925468942594</v>
       </c>
       <c r="E29">
-        <v>-2.211999999999996</v>
+        <v>-0.7680000000000007</v>
       </c>
       <c r="F29">
-        <v>38.98800000000001</v>
+        <v>40.432</v>
       </c>
       <c r="G29">
         <v>0.298</v>
@@ -3665,28 +3665,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M29">
-        <v>2.156036400000001</v>
+        <v>2.2358896</v>
       </c>
       <c r="N29">
-        <v>8.547296933333332</v>
+        <v>8.467443733333333</v>
       </c>
       <c r="O29">
-        <v>1.28209454</v>
+        <v>1.27011656</v>
       </c>
       <c r="P29">
-        <v>7.265202393333333</v>
+        <v>7.197327173333333</v>
       </c>
       <c r="Q29">
-        <v>12.89520239333333</v>
+        <v>12.82732717333333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09973674955592743</v>
+        <v>0.1004003798773121</v>
       </c>
       <c r="T29">
-        <v>0.7424596596986303</v>
+        <v>0.75159478086625</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.964356507772006</v>
+        <v>4.787058061065865</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08544967351166471</v>
+        <v>0.0854001698475024</v>
       </c>
       <c r="C30">
-        <v>123.0585468942594</v>
+        <v>121.8185518029847</v>
       </c>
       <c r="D30">
-        <v>163.1925468942594</v>
+        <v>163.3965518029847</v>
       </c>
       <c r="E30">
-        <v>-0.7680000000000007</v>
+        <v>0.6760000000000019</v>
       </c>
       <c r="F30">
-        <v>40.432</v>
+        <v>41.876</v>
       </c>
       <c r="G30">
         <v>0.298</v>
@@ -3747,28 +3747,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M30">
-        <v>2.2358896</v>
+        <v>2.3157428</v>
       </c>
       <c r="N30">
-        <v>8.467443733333333</v>
+        <v>8.387590533333332</v>
       </c>
       <c r="O30">
-        <v>1.27011656</v>
+        <v>1.25813858</v>
       </c>
       <c r="P30">
-        <v>7.197327173333333</v>
+        <v>7.129451953333333</v>
       </c>
       <c r="Q30">
-        <v>12.82732717333333</v>
+        <v>12.75945195333333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1004003798773121</v>
+        <v>0.1010827040105668</v>
       </c>
       <c r="T30">
-        <v>0.75159478086625</v>
+        <v>0.760987229390704</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.787058061065865</v>
+        <v>4.621987093442904</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0854001698475024</v>
+        <v>0.08598816618334007</v>
       </c>
       <c r="C31">
-        <v>121.8185518029847</v>
+        <v>117.983883532371</v>
       </c>
       <c r="D31">
-        <v>163.3965518029847</v>
+        <v>161.0058835323709</v>
       </c>
       <c r="E31">
-        <v>0.6759999999999948</v>
+        <v>2.119999999999997</v>
       </c>
       <c r="F31">
-        <v>41.876</v>
+        <v>43.32</v>
       </c>
       <c r="G31">
         <v>0.298</v>
@@ -3829,45 +3829,45 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M31">
-        <v>2.3157428</v>
+        <v>2.503896</v>
       </c>
       <c r="N31">
-        <v>8.387590533333334</v>
+        <v>8.199437333333332</v>
       </c>
       <c r="O31">
-        <v>1.25813858</v>
+        <v>1.2299156</v>
       </c>
       <c r="P31">
-        <v>7.129451953333334</v>
+        <v>6.969521733333332</v>
       </c>
       <c r="Q31">
-        <v>12.75945195333333</v>
+        <v>12.59952173333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1010827040105668</v>
+        <v>0.1017845231190573</v>
       </c>
       <c r="T31">
-        <v>0.760987229390704</v>
+        <v>0.7706480335872852</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.15</v>
       </c>
       <c r="W31">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.621987093442906</v>
+        <v>4.274671684979461</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08598816618334007</v>
+        <v>0.08595991251917777</v>
       </c>
       <c r="C32">
-        <v>117.983883532371</v>
+        <v>116.6531558448867</v>
       </c>
       <c r="D32">
-        <v>161.0058835323709</v>
+        <v>161.1191558448867</v>
       </c>
       <c r="E32">
-        <v>2.119999999999997</v>
+        <v>3.564</v>
       </c>
       <c r="F32">
-        <v>43.32</v>
+        <v>44.764</v>
       </c>
       <c r="G32">
         <v>0.298</v>
@@ -3911,28 +3911,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M32">
-        <v>2.503896</v>
+        <v>2.5873592</v>
       </c>
       <c r="N32">
-        <v>8.199437333333332</v>
+        <v>8.115974133333333</v>
       </c>
       <c r="O32">
-        <v>1.2299156</v>
+        <v>1.21739612</v>
       </c>
       <c r="P32">
-        <v>6.969521733333332</v>
+        <v>6.898578013333333</v>
       </c>
       <c r="Q32">
-        <v>12.59952173333333</v>
+        <v>12.52857801333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1017845231190573</v>
+        <v>0.1025066848104026</v>
       </c>
       <c r="T32">
-        <v>0.7706480335872852</v>
+        <v>0.7805888610939122</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.274671684979461</v>
+        <v>4.136779049980124</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08595991251917777</v>
+        <v>0.08593165885501544</v>
       </c>
       <c r="C33">
-        <v>116.6531558448867</v>
+        <v>115.32258765033</v>
       </c>
       <c r="D33">
-        <v>161.1191558448867</v>
+        <v>161.23258765033</v>
       </c>
       <c r="E33">
-        <v>3.564</v>
+        <v>5.008000000000003</v>
       </c>
       <c r="F33">
-        <v>44.764</v>
+        <v>46.20800000000001</v>
       </c>
       <c r="G33">
         <v>0.298</v>
@@ -3993,28 +3993,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M33">
-        <v>2.5873592</v>
+        <v>2.6708224</v>
       </c>
       <c r="N33">
-        <v>8.115974133333333</v>
+        <v>8.032510933333333</v>
       </c>
       <c r="O33">
-        <v>1.21739612</v>
+        <v>1.20487664</v>
       </c>
       <c r="P33">
-        <v>6.898578013333333</v>
+        <v>6.827634293333332</v>
       </c>
       <c r="Q33">
-        <v>12.52857801333333</v>
+        <v>12.45763429333333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1025066848104026</v>
+        <v>0.1032500865514933</v>
       </c>
       <c r="T33">
-        <v>0.7805888610939122</v>
+        <v>0.7908220658801459</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.136779049980124</v>
+        <v>4.007504704668245</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08593165885501544</v>
+        <v>0.08688515519085313</v>
       </c>
       <c r="C34">
-        <v>115.32258765033</v>
+        <v>110.1367329383769</v>
       </c>
       <c r="D34">
-        <v>161.23258765033</v>
+        <v>157.4907329383769</v>
       </c>
       <c r="E34">
-        <v>5.008000000000003</v>
+        <v>6.451999999999998</v>
       </c>
       <c r="F34">
-        <v>46.20800000000001</v>
+        <v>47.652</v>
       </c>
       <c r="G34">
         <v>0.298</v>
@@ -4075,45 +4075,45 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M34">
-        <v>2.6708224</v>
+        <v>2.9210676</v>
       </c>
       <c r="N34">
-        <v>8.032510933333333</v>
+        <v>7.782265733333332</v>
       </c>
       <c r="O34">
-        <v>1.20487664</v>
+        <v>1.16733986</v>
       </c>
       <c r="P34">
-        <v>6.827634293333332</v>
+        <v>6.614925873333332</v>
       </c>
       <c r="Q34">
-        <v>12.45763429333333</v>
+        <v>12.24492587333333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1032500865514933</v>
+        <v>0.104015679389333</v>
       </c>
       <c r="T34">
-        <v>0.7908220658801459</v>
+        <v>0.8013607394659689</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.15</v>
       </c>
       <c r="W34">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.007504704668245</v>
+        <v>3.664185427729687</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08688515519085313</v>
+        <v>0.08688665152669083</v>
       </c>
       <c r="C35">
-        <v>110.1367329383769</v>
+        <v>108.6869972792505</v>
       </c>
       <c r="D35">
-        <v>157.4907329383769</v>
+        <v>157.4849972792505</v>
       </c>
       <c r="E35">
-        <v>6.451999999999998</v>
+        <v>7.896000000000001</v>
       </c>
       <c r="F35">
-        <v>47.652</v>
+        <v>49.096</v>
       </c>
       <c r="G35">
         <v>0.298</v>
@@ -4157,28 +4157,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M35">
-        <v>2.9210676</v>
+        <v>3.0095848</v>
       </c>
       <c r="N35">
-        <v>7.782265733333332</v>
+        <v>7.693748533333332</v>
       </c>
       <c r="O35">
-        <v>1.16733986</v>
+        <v>1.15406228</v>
       </c>
       <c r="P35">
-        <v>6.614925873333332</v>
+        <v>6.539686253333333</v>
       </c>
       <c r="Q35">
-        <v>12.24492587333333</v>
+        <v>12.16968625333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.104015679389333</v>
+        <v>0.1048044720101376</v>
       </c>
       <c r="T35">
-        <v>0.8013607394659689</v>
+        <v>0.8122187667968167</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.664185427729687</v>
+        <v>3.556415268090579</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08688665152669083</v>
+        <v>0.08772114786252849</v>
       </c>
       <c r="C36">
-        <v>108.6869972792505</v>
+        <v>104.1080484555708</v>
       </c>
       <c r="D36">
-        <v>157.4849972792505</v>
+        <v>154.3500484555708</v>
       </c>
       <c r="E36">
-        <v>7.896000000000001</v>
+        <v>9.340000000000003</v>
       </c>
       <c r="F36">
-        <v>49.096</v>
+        <v>50.54000000000001</v>
       </c>
       <c r="G36">
         <v>0.298</v>
@@ -4239,45 +4239,45 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M36">
-        <v>3.0095848</v>
+        <v>3.239614</v>
       </c>
       <c r="N36">
-        <v>7.693748533333332</v>
+        <v>7.463719333333333</v>
       </c>
       <c r="O36">
-        <v>1.15406228</v>
+        <v>1.1195579</v>
       </c>
       <c r="P36">
-        <v>6.539686253333333</v>
+        <v>6.344161433333333</v>
       </c>
       <c r="Q36">
-        <v>12.16968625333333</v>
+        <v>11.97416143333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1048044720101376</v>
+        <v>0.1056175351731208</v>
       </c>
       <c r="T36">
-        <v>0.8122187667968167</v>
+        <v>0.823410887276306</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.15</v>
       </c>
       <c r="W36">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.556415268090579</v>
+        <v>3.303891554158406</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08772114786252849</v>
+        <v>0.08774644419836619</v>
       </c>
       <c r="C37">
-        <v>104.1080484555708</v>
+        <v>102.5709656988099</v>
       </c>
       <c r="D37">
-        <v>154.3500484555708</v>
+        <v>154.2569656988099</v>
       </c>
       <c r="E37">
-        <v>9.340000000000003</v>
+        <v>10.78400000000001</v>
       </c>
       <c r="F37">
-        <v>50.54000000000001</v>
+        <v>51.98400000000001</v>
       </c>
       <c r="G37">
         <v>0.298</v>
@@ -4321,28 +4321,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M37">
-        <v>3.239614</v>
+        <v>3.332174400000001</v>
       </c>
       <c r="N37">
-        <v>7.463719333333333</v>
+        <v>7.371158933333332</v>
       </c>
       <c r="O37">
-        <v>1.1195579</v>
+        <v>1.10567384</v>
       </c>
       <c r="P37">
-        <v>6.344161433333333</v>
+        <v>6.265485093333332</v>
       </c>
       <c r="Q37">
-        <v>11.97416143333333</v>
+        <v>11.89548509333333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1056175351731208</v>
+        <v>0.1064560065599472</v>
       </c>
       <c r="T37">
-        <v>0.823410887276306</v>
+        <v>0.8349527615207792</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.303891554158406</v>
+        <v>3.212116788765117</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08774644419836618</v>
+        <v>0.08777174053420388</v>
       </c>
       <c r="C38">
-        <v>102.57096569881</v>
+        <v>101.0339951438615</v>
       </c>
       <c r="D38">
-        <v>154.25696569881</v>
+        <v>154.1639951438615</v>
       </c>
       <c r="E38">
-        <v>10.784</v>
+        <v>12.228</v>
       </c>
       <c r="F38">
-        <v>51.984</v>
+        <v>53.428</v>
       </c>
       <c r="G38">
         <v>0.298</v>
@@ -4403,28 +4403,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M38">
-        <v>3.3321744</v>
+        <v>3.4247348</v>
       </c>
       <c r="N38">
-        <v>7.371158933333333</v>
+        <v>7.278598533333333</v>
       </c>
       <c r="O38">
-        <v>1.10567384</v>
+        <v>1.09178978</v>
       </c>
       <c r="P38">
-        <v>6.265485093333333</v>
+        <v>6.186808753333333</v>
       </c>
       <c r="Q38">
-        <v>11.89548509333333</v>
+        <v>11.81680875333333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1064560065599472</v>
+        <v>0.1073210960860379</v>
       </c>
       <c r="T38">
-        <v>0.8349527615207791</v>
+        <v>0.8468610444714262</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.212116788765117</v>
+        <v>3.125302821501196</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08777174053420388</v>
+        <v>0.08779703687004156</v>
       </c>
       <c r="C39">
-        <v>101.0339951438615</v>
+        <v>99.49713658797559</v>
       </c>
       <c r="D39">
-        <v>154.1639951438615</v>
+        <v>154.0711365879756</v>
       </c>
       <c r="E39">
-        <v>12.228</v>
+        <v>13.672</v>
       </c>
       <c r="F39">
-        <v>53.428</v>
+        <v>54.872</v>
       </c>
       <c r="G39">
         <v>0.298</v>
@@ -4485,28 +4485,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M39">
-        <v>3.4247348</v>
+        <v>3.5172952</v>
       </c>
       <c r="N39">
-        <v>7.278598533333333</v>
+        <v>7.186038133333333</v>
       </c>
       <c r="O39">
-        <v>1.09178978</v>
+        <v>1.07790572</v>
       </c>
       <c r="P39">
-        <v>6.186808753333333</v>
+        <v>6.108132413333333</v>
       </c>
       <c r="Q39">
-        <v>11.81680875333333</v>
+        <v>11.73813241333333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1073210960860379</v>
+        <v>0.1082140917258735</v>
       </c>
       <c r="T39">
-        <v>0.8468610444714262</v>
+        <v>0.8591534655817715</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.125302821501196</v>
+        <v>3.043058010409059</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08779703687004156</v>
+        <v>0.09040803320587926</v>
       </c>
       <c r="C40">
-        <v>99.49713658797559</v>
+        <v>89.03504849534625</v>
       </c>
       <c r="D40">
-        <v>154.0711365879756</v>
+        <v>145.0530484953462</v>
       </c>
       <c r="E40">
-        <v>13.672</v>
+        <v>15.116</v>
       </c>
       <c r="F40">
-        <v>54.872</v>
+        <v>56.316</v>
       </c>
       <c r="G40">
         <v>0.298</v>
@@ -4567,45 +4567,45 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M40">
-        <v>3.5172952</v>
+        <v>4.049120400000001</v>
       </c>
       <c r="N40">
-        <v>7.186038133333333</v>
+        <v>6.654212933333333</v>
       </c>
       <c r="O40">
-        <v>1.07790572</v>
+        <v>0.9981319399999998</v>
       </c>
       <c r="P40">
-        <v>6.108132413333333</v>
+        <v>5.656080993333333</v>
       </c>
       <c r="Q40">
-        <v>11.73813241333333</v>
+        <v>11.28608099333333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1082140917258735</v>
+        <v>0.1091363659112775</v>
       </c>
       <c r="T40">
-        <v>0.8591534655817715</v>
+        <v>0.8718489168924559</v>
       </c>
       <c r="U40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V40">
         <v>0.15</v>
       </c>
       <c r="W40">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.043058010409059</v>
+        <v>2.643372455245671</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09040803320587926</v>
+        <v>0.09049962954171695</v>
       </c>
       <c r="C41">
-        <v>89.03504849534625</v>
+        <v>87.29381274908887</v>
       </c>
       <c r="D41">
-        <v>145.0530484953462</v>
+        <v>144.7558127490889</v>
       </c>
       <c r="E41">
-        <v>15.116</v>
+        <v>16.56</v>
       </c>
       <c r="F41">
-        <v>56.316</v>
+        <v>57.76000000000001</v>
       </c>
       <c r="G41">
         <v>0.298</v>
@@ -4649,28 +4649,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M41">
-        <v>4.049120400000001</v>
+        <v>4.152944000000001</v>
       </c>
       <c r="N41">
-        <v>6.654212933333333</v>
+        <v>6.550389333333333</v>
       </c>
       <c r="O41">
-        <v>0.9981319399999998</v>
+        <v>0.9825583999999998</v>
       </c>
       <c r="P41">
-        <v>5.656080993333333</v>
+        <v>5.567830933333333</v>
       </c>
       <c r="Q41">
-        <v>11.28608099333333</v>
+        <v>11.19783093333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1091363659112775</v>
+        <v>0.1100893825695282</v>
       </c>
       <c r="T41">
-        <v>0.8718489168924559</v>
+        <v>0.8849675499134968</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.643372455245671</v>
+        <v>2.577288143864529</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09049962954171695</v>
+        <v>0.09059122587755461</v>
       </c>
       <c r="C42">
-        <v>87.29381274908887</v>
+        <v>85.5537926741915</v>
       </c>
       <c r="D42">
-        <v>144.7558127490889</v>
+        <v>144.4597926741915</v>
       </c>
       <c r="E42">
-        <v>16.56</v>
+        <v>18.004</v>
       </c>
       <c r="F42">
-        <v>57.76000000000001</v>
+        <v>59.20400000000001</v>
       </c>
       <c r="G42">
         <v>0.298</v>
@@ -4731,28 +4731,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M42">
-        <v>4.152944000000001</v>
+        <v>4.256767600000001</v>
       </c>
       <c r="N42">
-        <v>6.550389333333333</v>
+        <v>6.446565733333332</v>
       </c>
       <c r="O42">
-        <v>0.9825583999999998</v>
+        <v>0.9669848599999998</v>
       </c>
       <c r="P42">
-        <v>5.567830933333333</v>
+        <v>5.479580873333332</v>
       </c>
       <c r="Q42">
-        <v>11.19783093333333</v>
+        <v>11.10958087333333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1100893825695282</v>
+        <v>0.1110747048772112</v>
       </c>
       <c r="T42">
-        <v>0.8849675499134968</v>
+        <v>0.8985308823589795</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.577288143864529</v>
+        <v>2.514427457428809</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09059122587755461</v>
+        <v>0.09207512221339231</v>
       </c>
       <c r="C43">
-        <v>85.5537926741915</v>
+        <v>79.47742550211582</v>
       </c>
       <c r="D43">
-        <v>144.4597926741915</v>
+        <v>139.8274255021158</v>
       </c>
       <c r="E43">
-        <v>18.004</v>
+        <v>19.44800000000001</v>
       </c>
       <c r="F43">
-        <v>59.20400000000001</v>
+        <v>60.64800000000001</v>
       </c>
       <c r="G43">
         <v>0.298</v>
@@ -4813,45 +4813,45 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M43">
-        <v>4.256767600000001</v>
+        <v>4.597118400000001</v>
       </c>
       <c r="N43">
-        <v>6.446565733333332</v>
+        <v>6.106214933333332</v>
       </c>
       <c r="O43">
-        <v>0.9669848599999998</v>
+        <v>0.9159322399999997</v>
       </c>
       <c r="P43">
-        <v>5.479580873333332</v>
+        <v>5.190282693333332</v>
       </c>
       <c r="Q43">
-        <v>11.10958087333333</v>
+        <v>10.82028269333333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1110747048772112</v>
+        <v>0.1120940038161936</v>
       </c>
       <c r="T43">
-        <v>0.8985308823589795</v>
+        <v>0.912561915923272</v>
       </c>
       <c r="U43">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.15</v>
       </c>
       <c r="W43">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.514427457428809</v>
+        <v>2.328270103579088</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09207512221339233</v>
+        <v>0.09219986854923</v>
       </c>
       <c r="C44">
-        <v>79.47742550211581</v>
+        <v>77.65749859701053</v>
       </c>
       <c r="D44">
-        <v>139.8274255021158</v>
+        <v>139.4514985970105</v>
       </c>
       <c r="E44">
-        <v>19.448</v>
+        <v>20.892</v>
       </c>
       <c r="F44">
-        <v>60.648</v>
+        <v>62.092</v>
       </c>
       <c r="G44">
         <v>0.298</v>
@@ -4895,28 +4895,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M44">
-        <v>4.5971184</v>
+        <v>4.7065736</v>
       </c>
       <c r="N44">
-        <v>6.106214933333333</v>
+        <v>5.996759733333333</v>
       </c>
       <c r="O44">
-        <v>0.9159322399999998</v>
+        <v>0.8995139599999998</v>
       </c>
       <c r="P44">
-        <v>5.190282693333333</v>
+        <v>5.097245773333333</v>
       </c>
       <c r="Q44">
-        <v>10.82028269333333</v>
+        <v>10.72724577333333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1120940038161936</v>
+        <v>0.1131490676302281</v>
       </c>
       <c r="T44">
-        <v>0.9125619159232718</v>
+        <v>0.9270852664547324</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.328270103579088</v>
+        <v>2.274124287216784</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09219986854923</v>
+        <v>0.09232461488506769</v>
       </c>
       <c r="C45">
-        <v>77.65749859701053</v>
+        <v>75.83958763568336</v>
       </c>
       <c r="D45">
-        <v>139.4514985970105</v>
+        <v>139.0775876356834</v>
       </c>
       <c r="E45">
-        <v>20.892</v>
+        <v>22.336</v>
       </c>
       <c r="F45">
-        <v>62.092</v>
+        <v>63.536</v>
       </c>
       <c r="G45">
         <v>0.298</v>
@@ -4977,28 +4977,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M45">
-        <v>4.7065736</v>
+        <v>4.816028800000001</v>
       </c>
       <c r="N45">
-        <v>5.996759733333333</v>
+        <v>5.887304533333332</v>
       </c>
       <c r="O45">
-        <v>0.8995139599999998</v>
+        <v>0.8830956799999998</v>
       </c>
       <c r="P45">
-        <v>5.097245773333333</v>
+        <v>5.004208853333333</v>
       </c>
       <c r="Q45">
-        <v>10.72724577333333</v>
+        <v>10.63420885333333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1131490676302281</v>
+        <v>0.1142418122947637</v>
       </c>
       <c r="T45">
-        <v>0.9270852664547324</v>
+        <v>0.9421273080766024</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.274124287216784</v>
+        <v>2.222439644325493</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09232461488506769</v>
+        <v>0.09244936122090537</v>
       </c>
       <c r="C46">
-        <v>75.83958763568336</v>
+        <v>74.02367644546278</v>
       </c>
       <c r="D46">
-        <v>139.0775876356834</v>
+        <v>138.7056764454628</v>
       </c>
       <c r="E46">
-        <v>22.336</v>
+        <v>23.78</v>
       </c>
       <c r="F46">
-        <v>63.536</v>
+        <v>64.98</v>
       </c>
       <c r="G46">
         <v>0.298</v>
@@ -5059,28 +5059,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M46">
-        <v>4.816028800000001</v>
+        <v>4.925484000000001</v>
       </c>
       <c r="N46">
-        <v>5.887304533333332</v>
+        <v>5.777849333333332</v>
       </c>
       <c r="O46">
-        <v>0.8830956799999998</v>
+        <v>0.8666773999999998</v>
       </c>
       <c r="P46">
-        <v>5.004208853333333</v>
+        <v>4.911171933333333</v>
       </c>
       <c r="Q46">
-        <v>10.63420885333333</v>
+        <v>10.54117193333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1142418122947637</v>
+        <v>0.1153742931289188</v>
       </c>
       <c r="T46">
-        <v>0.9421273080766024</v>
+        <v>0.9577163330301767</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.222439644325493</v>
+        <v>2.173052096673815</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09244936122090537</v>
+        <v>0.09257410755674306</v>
       </c>
       <c r="C47">
-        <v>74.02367644546278</v>
+        <v>72.20974902620699</v>
       </c>
       <c r="D47">
-        <v>138.7056764454628</v>
+        <v>138.335749026207</v>
       </c>
       <c r="E47">
-        <v>23.78</v>
+        <v>25.224</v>
       </c>
       <c r="F47">
-        <v>64.98</v>
+        <v>66.42400000000001</v>
       </c>
       <c r="G47">
         <v>0.298</v>
@@ -5141,28 +5141,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M47">
-        <v>4.925484000000001</v>
+        <v>5.034939200000001</v>
       </c>
       <c r="N47">
-        <v>5.777849333333332</v>
+        <v>5.668394133333332</v>
       </c>
       <c r="O47">
-        <v>0.8666773999999998</v>
+        <v>0.8502591199999998</v>
       </c>
       <c r="P47">
-        <v>4.911171933333333</v>
+        <v>4.818135013333332</v>
       </c>
       <c r="Q47">
-        <v>10.54117193333333</v>
+        <v>10.44813501333333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1153742931289188</v>
+        <v>0.1165487176976723</v>
       </c>
       <c r="T47">
-        <v>0.9577163330301767</v>
+        <v>0.973882729278328</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.173052096673815</v>
+        <v>2.125811833702645</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09257410755674306</v>
+        <v>0.09269885389258073</v>
       </c>
       <c r="C48">
-        <v>72.20974902620699</v>
+        <v>70.39778954800938</v>
       </c>
       <c r="D48">
-        <v>138.335749026207</v>
+        <v>137.9677895480094</v>
       </c>
       <c r="E48">
-        <v>25.224</v>
+        <v>26.66800000000001</v>
       </c>
       <c r="F48">
-        <v>66.42400000000001</v>
+        <v>67.86800000000001</v>
       </c>
       <c r="G48">
         <v>0.298</v>
@@ -5223,28 +5223,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M48">
-        <v>5.034939200000001</v>
+        <v>5.144394400000001</v>
       </c>
       <c r="N48">
-        <v>5.668394133333332</v>
+        <v>5.558938933333332</v>
       </c>
       <c r="O48">
-        <v>0.8502591199999998</v>
+        <v>0.8338408399999998</v>
       </c>
       <c r="P48">
-        <v>4.818135013333332</v>
+        <v>4.725098093333332</v>
       </c>
       <c r="Q48">
-        <v>10.44813501333333</v>
+        <v>10.35509809333333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1165487176976723</v>
+        <v>0.1177674601746806</v>
       </c>
       <c r="T48">
-        <v>0.973882729278328</v>
+        <v>0.9906591782150885</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.125811833702645</v>
+        <v>2.080581794687696</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09269885389258073</v>
+        <v>0.09282360022841843</v>
       </c>
       <c r="C49">
-        <v>70.39778954800938</v>
+        <v>68.58778234894044</v>
       </c>
       <c r="D49">
-        <v>137.9677895480094</v>
+        <v>137.6017823489404</v>
       </c>
       <c r="E49">
-        <v>26.66800000000001</v>
+        <v>28.11200000000001</v>
       </c>
       <c r="F49">
-        <v>67.86800000000001</v>
+        <v>69.31200000000001</v>
       </c>
       <c r="G49">
         <v>0.298</v>
@@ -5305,28 +5305,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M49">
-        <v>5.144394400000001</v>
+        <v>5.253849600000001</v>
       </c>
       <c r="N49">
-        <v>5.558938933333332</v>
+        <v>5.449483733333332</v>
       </c>
       <c r="O49">
-        <v>0.8338408399999998</v>
+        <v>0.8174225599999997</v>
       </c>
       <c r="P49">
-        <v>4.725098093333332</v>
+        <v>4.632061173333332</v>
       </c>
       <c r="Q49">
-        <v>10.35509809333333</v>
+        <v>10.26206117333333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1177674601746806</v>
+        <v>0.1190330773623431</v>
       </c>
       <c r="T49">
-        <v>0.9906591782150885</v>
+        <v>1.008080875187878</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.080581794687696</v>
+        <v>2.037236340631702</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09282360022841843</v>
+        <v>0.09886264656425611</v>
       </c>
       <c r="C50">
-        <v>68.58778234894045</v>
+        <v>51.48335842920956</v>
       </c>
       <c r="D50">
-        <v>137.6017823489404</v>
+        <v>121.9413584292096</v>
       </c>
       <c r="E50">
-        <v>28.11199999999999</v>
+        <v>29.556</v>
       </c>
       <c r="F50">
-        <v>69.312</v>
+        <v>70.756</v>
       </c>
       <c r="G50">
         <v>0.298</v>
@@ -5387,45 +5387,45 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M50">
-        <v>5.253849600000001</v>
+        <v>6.36804</v>
       </c>
       <c r="N50">
-        <v>5.449483733333333</v>
+        <v>4.335293333333333</v>
       </c>
       <c r="O50">
-        <v>0.8174225599999999</v>
+        <v>0.650294</v>
       </c>
       <c r="P50">
-        <v>4.632061173333333</v>
+        <v>3.684999333333333</v>
       </c>
       <c r="Q50">
-        <v>10.26206117333333</v>
+        <v>9.314999333333333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1190330773623431</v>
+        <v>0.1203483265965806</v>
       </c>
       <c r="T50">
-        <v>1.008080875187878</v>
+        <v>1.026185775963523</v>
       </c>
       <c r="U50">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V50">
         <v>0.15</v>
       </c>
       <c r="W50">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.037236340631702</v>
+        <v>1.680789274774237</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09886264656425611</v>
+        <v>0.09910809290009379</v>
       </c>
       <c r="C51">
-        <v>51.48335842920956</v>
+        <v>49.47790409863333</v>
       </c>
       <c r="D51">
-        <v>121.9413584292096</v>
+        <v>121.3799040986333</v>
       </c>
       <c r="E51">
-        <v>29.556</v>
+        <v>31</v>
       </c>
       <c r="F51">
-        <v>70.756</v>
+        <v>72.2</v>
       </c>
       <c r="G51">
         <v>0.298</v>
@@ -5469,28 +5469,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M51">
-        <v>6.36804</v>
+        <v>6.498</v>
       </c>
       <c r="N51">
-        <v>4.335293333333333</v>
+        <v>4.205333333333333</v>
       </c>
       <c r="O51">
-        <v>0.650294</v>
+        <v>0.6307999999999999</v>
       </c>
       <c r="P51">
-        <v>3.684999333333333</v>
+        <v>3.574533333333333</v>
       </c>
       <c r="Q51">
-        <v>9.314999333333333</v>
+        <v>9.204533333333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1203483265965806</v>
+        <v>0.1217161858001876</v>
       </c>
       <c r="T51">
-        <v>1.026185775963523</v>
+        <v>1.045014872770193</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.680789274774237</v>
+        <v>1.647173489278752</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09910809290009379</v>
+        <v>0.09935353923593149</v>
       </c>
       <c r="C52">
-        <v>49.47790409863333</v>
+        <v>47.47759627789171</v>
       </c>
       <c r="D52">
-        <v>121.3799040986333</v>
+        <v>120.8235962778917</v>
       </c>
       <c r="E52">
-        <v>31</v>
+        <v>32.444</v>
       </c>
       <c r="F52">
-        <v>72.2</v>
+        <v>73.64400000000001</v>
       </c>
       <c r="G52">
         <v>0.298</v>
@@ -5551,28 +5551,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M52">
-        <v>6.498</v>
+        <v>6.62796</v>
       </c>
       <c r="N52">
-        <v>4.205333333333333</v>
+        <v>4.075373333333333</v>
       </c>
       <c r="O52">
-        <v>0.6307999999999999</v>
+        <v>0.611306</v>
       </c>
       <c r="P52">
-        <v>3.574533333333333</v>
+        <v>3.464067333333333</v>
       </c>
       <c r="Q52">
-        <v>9.204533333333334</v>
+        <v>9.094067333333333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1217161858001876</v>
+        <v>0.1231398759916969</v>
       </c>
       <c r="T52">
-        <v>1.045014872770193</v>
+        <v>1.064612504140401</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.647173489278752</v>
+        <v>1.61487596988113</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09935353923593149</v>
+        <v>0.09959898557176916</v>
       </c>
       <c r="C53">
-        <v>47.47759627789171</v>
+        <v>45.48236452744212</v>
       </c>
       <c r="D53">
-        <v>120.8235962778917</v>
+        <v>120.2723645274421</v>
       </c>
       <c r="E53">
-        <v>32.444</v>
+        <v>33.88800000000001</v>
       </c>
       <c r="F53">
-        <v>73.64400000000001</v>
+        <v>75.08800000000001</v>
       </c>
       <c r="G53">
         <v>0.298</v>
@@ -5633,28 +5633,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M53">
-        <v>6.62796</v>
+        <v>6.75792</v>
       </c>
       <c r="N53">
-        <v>4.075373333333333</v>
+        <v>3.945413333333333</v>
       </c>
       <c r="O53">
-        <v>0.611306</v>
+        <v>0.5918119999999999</v>
       </c>
       <c r="P53">
-        <v>3.464067333333333</v>
+        <v>3.353601333333333</v>
       </c>
       <c r="Q53">
-        <v>9.094067333333333</v>
+        <v>8.983601333333333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1231398759916969</v>
+        <v>0.1246228866078524</v>
       </c>
       <c r="T53">
-        <v>1.064612504140401</v>
+        <v>1.085026703484367</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.61487596988113</v>
+        <v>1.583820662768031</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09959898557176916</v>
+        <v>0.09984443190760686</v>
       </c>
       <c r="C54">
-        <v>45.48236452744212</v>
+        <v>43.4921396873649</v>
       </c>
       <c r="D54">
-        <v>120.2723645274421</v>
+        <v>119.7261396873649</v>
       </c>
       <c r="E54">
-        <v>33.88800000000001</v>
+        <v>35.33200000000001</v>
       </c>
       <c r="F54">
-        <v>75.08800000000001</v>
+        <v>76.53200000000001</v>
       </c>
       <c r="G54">
         <v>0.298</v>
@@ -5715,28 +5715,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M54">
-        <v>6.75792</v>
+        <v>6.887880000000001</v>
       </c>
       <c r="N54">
-        <v>3.945413333333333</v>
+        <v>3.815453333333332</v>
       </c>
       <c r="O54">
-        <v>0.5918119999999999</v>
+        <v>0.5723179999999998</v>
       </c>
       <c r="P54">
-        <v>3.353601333333333</v>
+        <v>3.243135333333333</v>
       </c>
       <c r="Q54">
-        <v>8.983601333333333</v>
+        <v>8.873135333333332</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1246228866078524</v>
+        <v>0.126169004058738</v>
       </c>
       <c r="T54">
-        <v>1.085026703484367</v>
+        <v>1.106309592162119</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.583820662768031</v>
+        <v>1.553937254036559</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09984443190760686</v>
+        <v>0.1000898782434445</v>
       </c>
       <c r="C55">
-        <v>43.4921396873649</v>
+        <v>41.50685384843777</v>
       </c>
       <c r="D55">
-        <v>119.7261396873649</v>
+        <v>119.1848538484378</v>
       </c>
       <c r="E55">
-        <v>35.33200000000001</v>
+        <v>36.77600000000001</v>
       </c>
       <c r="F55">
-        <v>76.53200000000001</v>
+        <v>77.97600000000001</v>
       </c>
       <c r="G55">
         <v>0.298</v>
@@ -5797,28 +5797,28 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M55">
-        <v>6.887880000000001</v>
+        <v>7.017840000000001</v>
       </c>
       <c r="N55">
-        <v>3.815453333333332</v>
+        <v>3.685493333333333</v>
       </c>
       <c r="O55">
-        <v>0.5723179999999998</v>
+        <v>0.5528239999999999</v>
       </c>
       <c r="P55">
-        <v>3.243135333333333</v>
+        <v>3.132669333333333</v>
       </c>
       <c r="Q55">
-        <v>8.873135333333332</v>
+        <v>8.762669333333333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.126169004058738</v>
+        <v>0.1277823440074881</v>
       </c>
       <c r="T55">
-        <v>1.106309592162119</v>
+        <v>1.128517823825861</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.553937254036559</v>
+        <v>1.525160638221067</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1000898782434445</v>
+        <v>0.1281593643403696</v>
       </c>
       <c r="C56">
-        <v>41.50685384843777</v>
+        <v>-0.5573916434636743</v>
       </c>
       <c r="D56">
-        <v>119.1848538484378</v>
+        <v>78.56460835653634</v>
       </c>
       <c r="E56">
-        <v>36.77600000000001</v>
+        <v>38.22000000000001</v>
       </c>
       <c r="F56">
-        <v>77.97600000000001</v>
+        <v>79.42000000000002</v>
       </c>
       <c r="G56">
         <v>0.298</v>
@@ -5879,45 +5879,45 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M56">
-        <v>7.017840000000001</v>
+        <v>11.658856</v>
       </c>
       <c r="N56">
-        <v>3.685493333333333</v>
+        <v>-0.9555226666666705</v>
       </c>
       <c r="O56">
-        <v>0.5528239999999999</v>
+        <v>-0.1433284000000006</v>
       </c>
       <c r="P56">
-        <v>3.132669333333333</v>
+        <v>-0.8121942666666699</v>
       </c>
       <c r="Q56">
-        <v>8.762669333333333</v>
+        <v>4.81780573333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1277823440074881</v>
+        <v>0.1300839675400025</v>
       </c>
       <c r="T56">
-        <v>1.128517823825861</v>
+        <v>1.160200538093487</v>
       </c>
       <c r="U56">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.15</v>
+        <v>0.1377064782342281</v>
       </c>
       <c r="W56">
-        <v>0.0765</v>
+        <v>0.1265846889952153</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.525160638221067</v>
+        <v>0.9180431882281872</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1281593643403696</v>
+        <v>0.1291693643403695</v>
       </c>
       <c r="C57">
-        <v>-0.5573916434636743</v>
+        <v>-2.95318316865918</v>
       </c>
       <c r="D57">
-        <v>78.56460835653634</v>
+        <v>77.61281683134082</v>
       </c>
       <c r="E57">
-        <v>38.22000000000001</v>
+        <v>39.664</v>
       </c>
       <c r="F57">
-        <v>79.42000000000002</v>
+        <v>80.864</v>
       </c>
       <c r="G57">
         <v>0.298</v>
@@ -5961,37 +5961,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M57">
-        <v>11.658856</v>
+        <v>11.8708352</v>
       </c>
       <c r="N57">
-        <v>-0.9555226666666705</v>
+        <v>-1.167501866666669</v>
       </c>
       <c r="O57">
-        <v>-0.1433284000000006</v>
+        <v>-0.1751252800000003</v>
       </c>
       <c r="P57">
-        <v>-0.8121942666666699</v>
+        <v>-0.9923765866666685</v>
       </c>
       <c r="Q57">
-        <v>4.81780573333333</v>
+        <v>4.637623413333332</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1300839675400025</v>
+        <v>0.1319995122568207</v>
       </c>
       <c r="T57">
-        <v>1.160200538093487</v>
+        <v>1.186568732141066</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1377064782342281</v>
+        <v>0.1352474339800455</v>
       </c>
       <c r="W57">
-        <v>0.1265846889952153</v>
+        <v>0.1269456766917293</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9180431882281872</v>
+        <v>0.9016495598669697</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1291693643403695</v>
+        <v>0.1301793643403696</v>
       </c>
       <c r="C58">
-        <v>-2.95318316865918</v>
+        <v>-5.326189278298131</v>
       </c>
       <c r="D58">
-        <v>77.61281683134082</v>
+        <v>76.68381072170187</v>
       </c>
       <c r="E58">
-        <v>39.664</v>
+        <v>41.108</v>
       </c>
       <c r="F58">
-        <v>80.864</v>
+        <v>82.30800000000001</v>
       </c>
       <c r="G58">
         <v>0.298</v>
@@ -6043,37 +6043,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M58">
-        <v>11.8708352</v>
+        <v>12.0828144</v>
       </c>
       <c r="N58">
-        <v>-1.167501866666669</v>
+        <v>-1.379481066666669</v>
       </c>
       <c r="O58">
-        <v>-0.1751252800000003</v>
+        <v>-0.2069221600000003</v>
       </c>
       <c r="P58">
-        <v>-0.9923765866666685</v>
+        <v>-1.172558906666668</v>
       </c>
       <c r="Q58">
-        <v>4.637623413333332</v>
+        <v>4.457441093333331</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1319995122568207</v>
+        <v>0.1340041520767468</v>
       </c>
       <c r="T58">
-        <v>1.186568732141066</v>
+        <v>1.214163353818766</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1352474339800455</v>
+        <v>0.1328746719803955</v>
       </c>
       <c r="W58">
-        <v>0.1269456766917293</v>
+        <v>0.127293998153278</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9016495598669697</v>
+        <v>0.8858311465359703</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1301793643403696</v>
+        <v>0.1311893643403695</v>
       </c>
       <c r="C59">
-        <v>-5.326189278298131</v>
+        <v>-7.677218501752634</v>
       </c>
       <c r="D59">
-        <v>76.68381072170187</v>
+        <v>75.77678149824737</v>
       </c>
       <c r="E59">
-        <v>41.108</v>
+        <v>42.55200000000001</v>
       </c>
       <c r="F59">
-        <v>82.30800000000001</v>
+        <v>83.75200000000001</v>
       </c>
       <c r="G59">
         <v>0.298</v>
@@ -6125,37 +6125,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M59">
-        <v>12.0828144</v>
+        <v>12.2947936</v>
       </c>
       <c r="N59">
-        <v>-1.379481066666669</v>
+        <v>-1.591460266666669</v>
       </c>
       <c r="O59">
-        <v>-0.2069221600000003</v>
+        <v>-0.2387190400000003</v>
       </c>
       <c r="P59">
-        <v>-1.172558906666668</v>
+        <v>-1.352741226666669</v>
       </c>
       <c r="Q59">
-        <v>4.457441093333331</v>
+        <v>4.277258773333331</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1340041520767468</v>
+        <v>0.1361042509357169</v>
       </c>
       <c r="T59">
-        <v>1.214163353818766</v>
+        <v>1.243072005100164</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1328746719803955</v>
+        <v>0.1305837293600439</v>
       </c>
       <c r="W59">
-        <v>0.127293998153278</v>
+        <v>0.1276303085299456</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8858311465359703</v>
+        <v>0.8705581957336259</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1311893643403695</v>
+        <v>0.1321993643403695</v>
       </c>
       <c r="C60">
-        <v>-7.67721850175262</v>
+        <v>-10.0070415618821</v>
       </c>
       <c r="D60">
-        <v>75.77678149824737</v>
+        <v>74.89095843811789</v>
       </c>
       <c r="E60">
-        <v>42.55199999999999</v>
+        <v>43.996</v>
       </c>
       <c r="F60">
-        <v>83.752</v>
+        <v>85.196</v>
       </c>
       <c r="G60">
         <v>0.298</v>
@@ -6207,37 +6207,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M60">
-        <v>12.2947936</v>
+        <v>12.5067728</v>
       </c>
       <c r="N60">
-        <v>-1.591460266666667</v>
+        <v>-1.803439466666667</v>
       </c>
       <c r="O60">
-        <v>-0.23871904</v>
+        <v>-0.2705159200000001</v>
       </c>
       <c r="P60">
-        <v>-1.352741226666667</v>
+        <v>-1.532923546666667</v>
       </c>
       <c r="Q60">
-        <v>4.277258773333333</v>
+        <v>4.097076453333333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1361042509357169</v>
+        <v>0.1383067936414661</v>
       </c>
       <c r="T60">
-        <v>1.243072005100164</v>
+        <v>1.273390834492851</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1305837293600439</v>
+        <v>0.1283704458115686</v>
       </c>
       <c r="W60">
-        <v>0.1276303085299456</v>
+        <v>0.1279552185548617</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.870558195733626</v>
+        <v>0.8558029720771239</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1321993643403695</v>
+        <v>0.1332093643403695</v>
       </c>
       <c r="C61">
-        <v>-10.0070415618821</v>
+        <v>-12.31639355927177</v>
       </c>
       <c r="D61">
-        <v>74.89095843811789</v>
+        <v>74.02560644072823</v>
       </c>
       <c r="E61">
-        <v>43.996</v>
+        <v>45.44</v>
       </c>
       <c r="F61">
-        <v>85.196</v>
+        <v>86.64</v>
       </c>
       <c r="G61">
         <v>0.298</v>
@@ -6289,37 +6289,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M61">
-        <v>12.5067728</v>
+        <v>12.718752</v>
       </c>
       <c r="N61">
-        <v>-1.803439466666667</v>
+        <v>-2.015418666666669</v>
       </c>
       <c r="O61">
-        <v>-0.2705159200000001</v>
+        <v>-0.3023128000000003</v>
       </c>
       <c r="P61">
-        <v>-1.532923546666667</v>
+        <v>-1.713105866666669</v>
       </c>
       <c r="Q61">
-        <v>4.097076453333333</v>
+        <v>3.916894133333331</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1383067936414661</v>
+        <v>0.1406194634825028</v>
       </c>
       <c r="T61">
-        <v>1.273390834492851</v>
+        <v>1.305225605355173</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1283704458115686</v>
+        <v>0.1262309383813758</v>
       </c>
       <c r="W61">
-        <v>0.1279552185548617</v>
+        <v>0.1282692982456141</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8558029720771239</v>
+        <v>0.8415395892091717</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1332093643403695</v>
+        <v>0.1342193643403695</v>
       </c>
       <c r="C62">
-        <v>-12.31639355927177</v>
+        <v>-14.60597600676965</v>
       </c>
       <c r="D62">
-        <v>74.02560644072823</v>
+        <v>73.18002399323035</v>
       </c>
       <c r="E62">
-        <v>45.44</v>
+        <v>46.884</v>
       </c>
       <c r="F62">
-        <v>86.64</v>
+        <v>88.084</v>
       </c>
       <c r="G62">
         <v>0.298</v>
@@ -6371,37 +6371,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M62">
-        <v>12.718752</v>
+        <v>12.9307312</v>
       </c>
       <c r="N62">
-        <v>-2.015418666666669</v>
+        <v>-2.227397866666669</v>
       </c>
       <c r="O62">
-        <v>-0.3023128000000003</v>
+        <v>-0.3341096800000004</v>
       </c>
       <c r="P62">
-        <v>-1.713105866666669</v>
+        <v>-1.893288186666669</v>
       </c>
       <c r="Q62">
-        <v>3.916894133333331</v>
+        <v>3.736711813333331</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1406194634825028</v>
+        <v>0.1430507317769259</v>
       </c>
       <c r="T62">
-        <v>1.305225605355173</v>
+        <v>1.338692928569408</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1262309383813758</v>
+        <v>0.1241615787357794</v>
       </c>
       <c r="W62">
-        <v>0.1282692982456141</v>
+        <v>0.1285730802415876</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8415395892091717</v>
+        <v>0.8277438582385296</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1342193643403695</v>
+        <v>0.1352293643403695</v>
       </c>
       <c r="C63">
-        <v>-14.60597600676965</v>
+        <v>-16.87645872615758</v>
       </c>
       <c r="D63">
-        <v>73.18002399323035</v>
+        <v>72.35354127384242</v>
       </c>
       <c r="E63">
-        <v>46.884</v>
+        <v>48.328</v>
       </c>
       <c r="F63">
-        <v>88.084</v>
+        <v>89.52800000000001</v>
       </c>
       <c r="G63">
         <v>0.298</v>
@@ -6453,37 +6453,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M63">
-        <v>12.9307312</v>
+        <v>13.1427104</v>
       </c>
       <c r="N63">
-        <v>-2.227397866666669</v>
+        <v>-2.439377066666669</v>
       </c>
       <c r="O63">
-        <v>-0.3341096800000004</v>
+        <v>-0.3659065600000003</v>
       </c>
       <c r="P63">
-        <v>-1.893288186666669</v>
+        <v>-2.073470506666669</v>
       </c>
       <c r="Q63">
-        <v>3.736711813333331</v>
+        <v>3.556529493333331</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1430507317769259</v>
+        <v>0.1456099615605292</v>
       </c>
       <c r="T63">
-        <v>1.338692928569408</v>
+        <v>1.37392168984755</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1241615787357794</v>
+        <v>0.1221589726271378</v>
       </c>
       <c r="W63">
-        <v>0.1285730802415876</v>
+        <v>0.1288670628183362</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8277438582385296</v>
+        <v>0.8143931508475856</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1352293643403695</v>
+        <v>0.1362393643403695</v>
       </c>
       <c r="C64">
-        <v>-16.87645872615758</v>
+        <v>-19.12848161773337</v>
       </c>
       <c r="D64">
-        <v>72.35354127384242</v>
+        <v>71.54551838226664</v>
       </c>
       <c r="E64">
-        <v>48.328</v>
+        <v>49.77200000000001</v>
       </c>
       <c r="F64">
-        <v>89.52800000000001</v>
+        <v>90.97200000000001</v>
       </c>
       <c r="G64">
         <v>0.298</v>
@@ -6535,37 +6535,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M64">
-        <v>13.1427104</v>
+        <v>13.3546896</v>
       </c>
       <c r="N64">
-        <v>-2.439377066666669</v>
+        <v>-2.651356266666669</v>
       </c>
       <c r="O64">
-        <v>-0.3659065600000003</v>
+        <v>-0.3977034400000004</v>
       </c>
       <c r="P64">
-        <v>-2.073470506666669</v>
+        <v>-2.253652826666669</v>
       </c>
       <c r="Q64">
-        <v>3.556529493333331</v>
+        <v>3.376347173333331</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1456099615605292</v>
+        <v>0.1483075280891922</v>
       </c>
       <c r="T64">
-        <v>1.37392168984755</v>
+        <v>1.411054708492078</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1221589726271378</v>
+        <v>0.120219941315596</v>
       </c>
       <c r="W64">
-        <v>0.1288670628183362</v>
+        <v>0.1291517126148705</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8143931508475856</v>
+        <v>0.8014662754373064</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1362393643403695</v>
+        <v>0.1726451785765312</v>
       </c>
       <c r="C65">
-        <v>-19.12848161773337</v>
+        <v>-41.10674930440917</v>
       </c>
       <c r="D65">
-        <v>71.54551838226664</v>
+        <v>51.01125069559084</v>
       </c>
       <c r="E65">
-        <v>49.77200000000001</v>
+        <v>51.21600000000001</v>
       </c>
       <c r="F65">
-        <v>90.97200000000001</v>
+        <v>92.41600000000001</v>
       </c>
       <c r="G65">
         <v>0.298</v>
@@ -6617,45 +6617,45 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M65">
-        <v>13.3546896</v>
+        <v>18.5571328</v>
       </c>
       <c r="N65">
-        <v>-2.651356266666669</v>
+        <v>-7.853799466666668</v>
       </c>
       <c r="O65">
-        <v>-0.3977034400000004</v>
+        <v>-1.17806992</v>
       </c>
       <c r="P65">
-        <v>-2.253652826666669</v>
+        <v>-6.675729546666668</v>
       </c>
       <c r="Q65">
-        <v>3.376347173333331</v>
+        <v>-1.045729546666668</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1483075280891922</v>
+        <v>0.1534766656365631</v>
       </c>
       <c r="T65">
-        <v>1.411054708492078</v>
+        <v>1.482209832520769</v>
       </c>
       <c r="U65">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.120219941315596</v>
+        <v>0.08651659808135875</v>
       </c>
       <c r="W65">
-        <v>0.1291517126148705</v>
+        <v>0.1834274671052632</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.8014662754373064</v>
+        <v>0.5767773205423918</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1726451785765312</v>
+        <v>0.1741951785765312</v>
       </c>
       <c r="C66">
-        <v>-41.10674930440917</v>
+        <v>-43.16656244828854</v>
       </c>
       <c r="D66">
-        <v>51.01125069559084</v>
+        <v>50.39543755171147</v>
       </c>
       <c r="E66">
-        <v>51.21600000000001</v>
+        <v>52.66000000000001</v>
       </c>
       <c r="F66">
-        <v>92.41600000000001</v>
+        <v>93.86000000000001</v>
       </c>
       <c r="G66">
         <v>0.298</v>
@@ -6699,37 +6699,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M66">
-        <v>18.5571328</v>
+        <v>18.847088</v>
       </c>
       <c r="N66">
-        <v>-7.853799466666668</v>
+        <v>-8.14375466666667</v>
       </c>
       <c r="O66">
-        <v>-1.17806992</v>
+        <v>-1.221563200000001</v>
       </c>
       <c r="P66">
-        <v>-6.675729546666668</v>
+        <v>-6.92219146666667</v>
       </c>
       <c r="Q66">
-        <v>-1.045729546666668</v>
+        <v>-1.29219146666667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1534766656365631</v>
+        <v>0.1565531417976078</v>
       </c>
       <c r="T66">
-        <v>1.482209832520769</v>
+        <v>1.524558684878506</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.08651659808135875</v>
+        <v>0.0851855734954917</v>
       </c>
       <c r="W66">
-        <v>0.1834274671052632</v>
+        <v>0.1836947368421053</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5767773205423918</v>
+        <v>0.567903823303278</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1741951785765312</v>
+        <v>0.1757451785765312</v>
       </c>
       <c r="C67">
-        <v>-43.16656244828854</v>
+        <v>-45.21168462196847</v>
       </c>
       <c r="D67">
-        <v>50.39543755171147</v>
+        <v>49.79431537803153</v>
       </c>
       <c r="E67">
-        <v>52.66000000000001</v>
+        <v>54.104</v>
       </c>
       <c r="F67">
-        <v>93.86000000000001</v>
+        <v>95.304</v>
       </c>
       <c r="G67">
         <v>0.298</v>
@@ -6781,37 +6781,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M67">
-        <v>18.847088</v>
+        <v>19.1370432</v>
       </c>
       <c r="N67">
-        <v>-8.14375466666667</v>
+        <v>-8.433709866666668</v>
       </c>
       <c r="O67">
-        <v>-1.221563200000001</v>
+        <v>-1.26505648</v>
       </c>
       <c r="P67">
-        <v>-6.92219146666667</v>
+        <v>-7.168653386666668</v>
       </c>
       <c r="Q67">
-        <v>-1.29219146666667</v>
+        <v>-1.538653386666668</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1565531417976078</v>
+        <v>0.1598105871445963</v>
       </c>
       <c r="T67">
-        <v>1.524558684878506</v>
+        <v>1.569398646198462</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.0851855734954917</v>
+        <v>0.08389488298798425</v>
       </c>
       <c r="W67">
-        <v>0.1836947368421053</v>
+        <v>0.1839539074960128</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.567903823303278</v>
+        <v>0.5592992199198951</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1757451785765312</v>
+        <v>0.1772951785765312</v>
       </c>
       <c r="C68">
-        <v>-45.21168462196847</v>
+        <v>-47.24263533507793</v>
       </c>
       <c r="D68">
-        <v>49.79431537803153</v>
+        <v>49.20736466492207</v>
       </c>
       <c r="E68">
-        <v>54.104</v>
+        <v>55.548</v>
       </c>
       <c r="F68">
-        <v>95.304</v>
+        <v>96.748</v>
       </c>
       <c r="G68">
         <v>0.298</v>
@@ -6863,37 +6863,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M68">
-        <v>19.1370432</v>
+        <v>19.4269984</v>
       </c>
       <c r="N68">
-        <v>-8.433709866666668</v>
+        <v>-8.723665066666669</v>
       </c>
       <c r="O68">
-        <v>-1.26505648</v>
+        <v>-1.30854976</v>
       </c>
       <c r="P68">
-        <v>-7.168653386666668</v>
+        <v>-7.415115306666669</v>
       </c>
       <c r="Q68">
-        <v>-1.538653386666668</v>
+        <v>-1.785115306666669</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1598105871445963</v>
+        <v>0.1632654534217053</v>
       </c>
       <c r="T68">
-        <v>1.569398646198462</v>
+        <v>1.616956180931749</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.08389488298798425</v>
+        <v>0.08264272055532777</v>
       </c>
       <c r="W68">
-        <v>0.1839539074960128</v>
+        <v>0.1842053417124902</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5592992199198951</v>
+        <v>0.5509514703688518</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1772951785765312</v>
+        <v>0.1788451785765312</v>
       </c>
       <c r="C69">
-        <v>-47.24263533507793</v>
+        <v>-49.2599098877274</v>
       </c>
       <c r="D69">
-        <v>49.20736466492207</v>
+        <v>48.6340901122726</v>
       </c>
       <c r="E69">
-        <v>55.548</v>
+        <v>56.992</v>
       </c>
       <c r="F69">
-        <v>96.748</v>
+        <v>98.19200000000001</v>
       </c>
       <c r="G69">
         <v>0.298</v>
@@ -6945,37 +6945,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M69">
-        <v>19.4269984</v>
+        <v>19.7169536</v>
       </c>
       <c r="N69">
-        <v>-8.723665066666669</v>
+        <v>-9.01362026666667</v>
       </c>
       <c r="O69">
-        <v>-1.30854976</v>
+        <v>-1.352043040000001</v>
       </c>
       <c r="P69">
-        <v>-7.415115306666669</v>
+        <v>-7.66157722666667</v>
       </c>
       <c r="Q69">
-        <v>-1.785115306666669</v>
+        <v>-2.03157722666667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1632654534217053</v>
+        <v>0.1669362488411336</v>
       </c>
       <c r="T69">
-        <v>1.616956180931749</v>
+        <v>1.667486061585866</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.08264272055532777</v>
+        <v>0.08142738642951412</v>
       </c>
       <c r="W69">
-        <v>0.1842053417124902</v>
+        <v>0.1844493808049536</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5509514703688518</v>
+        <v>0.5428492428634275</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1788451785765312</v>
+        <v>0.1803951785765312</v>
       </c>
       <c r="C70">
-        <v>-49.2599098877274</v>
+        <v>-51.2639807644948</v>
       </c>
       <c r="D70">
-        <v>48.6340901122726</v>
+        <v>48.0740192355052</v>
       </c>
       <c r="E70">
-        <v>56.992</v>
+        <v>58.43600000000001</v>
       </c>
       <c r="F70">
-        <v>98.19200000000001</v>
+        <v>99.63600000000001</v>
       </c>
       <c r="G70">
         <v>0.298</v>
@@ -7027,37 +7027,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M70">
-        <v>19.7169536</v>
+        <v>20.0069088</v>
       </c>
       <c r="N70">
-        <v>-9.01362026666667</v>
+        <v>-9.303575466666668</v>
       </c>
       <c r="O70">
-        <v>-1.352043040000001</v>
+        <v>-1.39553632</v>
       </c>
       <c r="P70">
-        <v>-7.66157722666667</v>
+        <v>-7.908039146666669</v>
       </c>
       <c r="Q70">
-        <v>-2.03157722666667</v>
+        <v>-2.278039146666669</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1669362488411336</v>
+        <v>0.1708438697714927</v>
       </c>
       <c r="T70">
-        <v>1.667486061585866</v>
+        <v>1.721275934540248</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.08142738642951412</v>
+        <v>0.08024727937981103</v>
       </c>
       <c r="W70">
-        <v>0.1844493808049536</v>
+        <v>0.184686346300534</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5428492428634275</v>
+        <v>0.5349818625320735</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1803951785765312</v>
+        <v>0.1819451785765312</v>
       </c>
       <c r="C71">
-        <v>-51.2639807644948</v>
+        <v>-53.25529893318885</v>
       </c>
       <c r="D71">
-        <v>48.0740192355052</v>
+        <v>47.52670106681116</v>
       </c>
       <c r="E71">
-        <v>58.43600000000001</v>
+        <v>59.88000000000001</v>
       </c>
       <c r="F71">
-        <v>99.63600000000001</v>
+        <v>101.08</v>
       </c>
       <c r="G71">
         <v>0.298</v>
@@ -7109,37 +7109,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M71">
-        <v>20.0069088</v>
+        <v>20.296864</v>
       </c>
       <c r="N71">
-        <v>-9.303575466666668</v>
+        <v>-9.59353066666667</v>
       </c>
       <c r="O71">
-        <v>-1.39553632</v>
+        <v>-1.4390296</v>
       </c>
       <c r="P71">
-        <v>-7.908039146666669</v>
+        <v>-8.154501066666668</v>
       </c>
       <c r="Q71">
-        <v>-2.278039146666669</v>
+        <v>-2.524501066666669</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1708438697714927</v>
+        <v>0.1750119987638758</v>
       </c>
       <c r="T71">
-        <v>1.721275934540248</v>
+        <v>1.778651799024923</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08024727937981103</v>
+        <v>0.07910088967438515</v>
       </c>
       <c r="W71">
-        <v>0.184686346300534</v>
+        <v>0.1849165413533835</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5349818625320735</v>
+        <v>0.527339264495901</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1819451785765312</v>
+        <v>0.1834951785765312</v>
       </c>
       <c r="C72">
-        <v>-53.25529893318885</v>
+        <v>-55.23429505589344</v>
       </c>
       <c r="D72">
-        <v>47.52670106681116</v>
+        <v>46.99170494410657</v>
       </c>
       <c r="E72">
-        <v>59.88000000000001</v>
+        <v>61.32400000000001</v>
       </c>
       <c r="F72">
-        <v>101.08</v>
+        <v>102.524</v>
       </c>
       <c r="G72">
         <v>0.298</v>
@@ -7191,37 +7191,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M72">
-        <v>20.296864</v>
+        <v>20.5868192</v>
       </c>
       <c r="N72">
-        <v>-9.59353066666667</v>
+        <v>-9.883485866666671</v>
       </c>
       <c r="O72">
-        <v>-1.4390296</v>
+        <v>-1.482522880000001</v>
       </c>
       <c r="P72">
-        <v>-8.154501066666668</v>
+        <v>-8.40096298666667</v>
       </c>
       <c r="Q72">
-        <v>-2.524501066666669</v>
+        <v>-2.77096298666667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1750119987638758</v>
+        <v>0.1794675849281474</v>
       </c>
       <c r="T72">
-        <v>1.778651799024923</v>
+        <v>1.839984619680956</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.07910088967438515</v>
+        <v>0.07798679263671775</v>
       </c>
       <c r="W72">
-        <v>0.1849165413533835</v>
+        <v>0.1851402520385471</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.527339264495901</v>
+        <v>0.5199119509114517</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1834951785765311</v>
+        <v>0.1850451785765312</v>
       </c>
       <c r="C73">
-        <v>-55.23429505589341</v>
+        <v>-57.2013806191277</v>
       </c>
       <c r="D73">
-        <v>46.99170494410659</v>
+        <v>46.4686193808723</v>
       </c>
       <c r="E73">
-        <v>61.324</v>
+        <v>62.768</v>
       </c>
       <c r="F73">
-        <v>102.524</v>
+        <v>103.968</v>
       </c>
       <c r="G73">
         <v>0.298</v>
@@ -7273,37 +7273,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M73">
-        <v>20.5868192</v>
+        <v>20.8767744</v>
       </c>
       <c r="N73">
-        <v>-9.883485866666668</v>
+        <v>-10.17344106666667</v>
       </c>
       <c r="O73">
-        <v>-1.48252288</v>
+        <v>-1.52601616</v>
       </c>
       <c r="P73">
-        <v>-8.400962986666668</v>
+        <v>-8.647424906666668</v>
       </c>
       <c r="Q73">
-        <v>-2.770962986666668</v>
+        <v>-3.017424906666668</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1794675849281473</v>
+        <v>0.1842414272470098</v>
       </c>
       <c r="T73">
-        <v>1.839984619680955</v>
+        <v>1.905698356098132</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.07798679263671777</v>
+        <v>0.07690364273898556</v>
       </c>
       <c r="W73">
-        <v>0.1851402520385471</v>
+        <v>0.1853577485380117</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5199119509114518</v>
+        <v>0.5126909515932372</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1850451785765312</v>
+        <v>0.1865951785765312</v>
       </c>
       <c r="C74">
-        <v>-57.2013806191277</v>
+        <v>-59.15694898935568</v>
       </c>
       <c r="D74">
-        <v>46.4686193808723</v>
+        <v>45.95705101064433</v>
       </c>
       <c r="E74">
-        <v>62.768</v>
+        <v>64.212</v>
       </c>
       <c r="F74">
-        <v>103.968</v>
+        <v>105.412</v>
       </c>
       <c r="G74">
         <v>0.298</v>
@@ -7355,37 +7355,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M74">
-        <v>20.8767744</v>
+        <v>21.1667296</v>
       </c>
       <c r="N74">
-        <v>-10.17344106666667</v>
+        <v>-10.46339626666667</v>
       </c>
       <c r="O74">
-        <v>-1.52601616</v>
+        <v>-1.56950944</v>
       </c>
       <c r="P74">
-        <v>-8.647424906666668</v>
+        <v>-8.89388682666667</v>
       </c>
       <c r="Q74">
-        <v>-3.017424906666668</v>
+        <v>-3.26388682666667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1842414272470098</v>
+        <v>0.1893688875154175</v>
       </c>
       <c r="T74">
-        <v>1.905698356098132</v>
+        <v>1.976279776694359</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.07690364273898556</v>
+        <v>0.07585016818091726</v>
       </c>
       <c r="W74">
-        <v>0.1853577485380117</v>
+        <v>0.1855692862292718</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5126909515932372</v>
+        <v>0.5056677878727818</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1865951785765312</v>
+        <v>0.2143824397163388</v>
       </c>
       <c r="C75">
-        <v>-59.15694898935568</v>
+        <v>-68.1759999839728</v>
       </c>
       <c r="D75">
-        <v>45.95705101064433</v>
+        <v>38.38200001602721</v>
       </c>
       <c r="E75">
-        <v>64.212</v>
+        <v>65.65600000000001</v>
       </c>
       <c r="F75">
-        <v>105.412</v>
+        <v>106.856</v>
       </c>
       <c r="G75">
         <v>0.298</v>
@@ -7437,45 +7437,45 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M75">
-        <v>21.1667296</v>
+        <v>25.1966448</v>
       </c>
       <c r="N75">
-        <v>-10.46339626666667</v>
+        <v>-14.49331146666667</v>
       </c>
       <c r="O75">
-        <v>-1.56950944</v>
+        <v>-2.17399672</v>
       </c>
       <c r="P75">
-        <v>-8.89388682666667</v>
+        <v>-12.31931474666667</v>
       </c>
       <c r="Q75">
-        <v>-3.26388682666667</v>
+        <v>-6.689314746666668</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1893688875154175</v>
+        <v>0.1961879260345013</v>
       </c>
       <c r="T75">
-        <v>1.976279776694359</v>
+        <v>2.070146408629624</v>
       </c>
       <c r="U75">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07585016818091726</v>
+        <v>0.06371880116355809</v>
       </c>
       <c r="W75">
-        <v>0.1855692862292718</v>
+        <v>0.220775106685633</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.5056677878727818</v>
+        <v>0.4247920077570539</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2143824397163388</v>
+        <v>0.2162824397163388</v>
       </c>
       <c r="C76">
-        <v>-68.1759999839728</v>
+        <v>-70.0477613425725</v>
       </c>
       <c r="D76">
-        <v>38.38200001602721</v>
+        <v>37.9542386574275</v>
       </c>
       <c r="E76">
-        <v>65.65600000000001</v>
+        <v>67.10000000000001</v>
       </c>
       <c r="F76">
-        <v>106.856</v>
+        <v>108.3</v>
       </c>
       <c r="G76">
         <v>0.298</v>
@@ -7519,37 +7519,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M76">
-        <v>25.1966448</v>
+        <v>25.53714</v>
       </c>
       <c r="N76">
-        <v>-14.49331146666667</v>
+        <v>-14.83380666666667</v>
       </c>
       <c r="O76">
-        <v>-2.17399672</v>
+        <v>-2.225071000000001</v>
       </c>
       <c r="P76">
-        <v>-12.31931474666667</v>
+        <v>-12.60873566666667</v>
       </c>
       <c r="Q76">
-        <v>-6.689314746666668</v>
+        <v>-6.978735666666672</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1961879260345013</v>
+        <v>0.2022034430758814</v>
       </c>
       <c r="T76">
-        <v>2.070146408629624</v>
+        <v>2.15295226497481</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06371880116355809</v>
+        <v>0.06286921714804397</v>
       </c>
       <c r="W76">
-        <v>0.220775106685633</v>
+        <v>0.2209754385964912</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4247920077570539</v>
+        <v>0.4191281143202932</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2162824397163388</v>
+        <v>0.2181824397163388</v>
       </c>
       <c r="C77">
-        <v>-70.0477613425725</v>
+        <v>-71.91009312606376</v>
       </c>
       <c r="D77">
-        <v>37.9542386574275</v>
+        <v>37.53590687393624</v>
       </c>
       <c r="E77">
-        <v>67.10000000000001</v>
+        <v>68.544</v>
       </c>
       <c r="F77">
-        <v>108.3</v>
+        <v>109.744</v>
       </c>
       <c r="G77">
         <v>0.298</v>
@@ -7601,37 +7601,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M77">
-        <v>25.53714</v>
+        <v>25.8776352</v>
       </c>
       <c r="N77">
-        <v>-14.83380666666667</v>
+        <v>-15.17430186666667</v>
       </c>
       <c r="O77">
-        <v>-2.225071000000001</v>
+        <v>-2.27614528</v>
       </c>
       <c r="P77">
-        <v>-12.60873566666667</v>
+        <v>-12.89815658666667</v>
       </c>
       <c r="Q77">
-        <v>-6.978735666666672</v>
+        <v>-7.268156586666668</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2022034430758814</v>
+        <v>0.2087202532040431</v>
       </c>
       <c r="T77">
-        <v>2.15295226497481</v>
+        <v>2.24265860934876</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06286921714804397</v>
+        <v>0.06204199060662235</v>
       </c>
       <c r="W77">
-        <v>0.2209754385964912</v>
+        <v>0.2211704986149585</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4191281143202932</v>
+        <v>0.4136132707108157</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2181824397163388</v>
+        <v>0.2200824397163388</v>
       </c>
       <c r="C78">
-        <v>-71.91009312606376</v>
+        <v>-73.76330373372198</v>
       </c>
       <c r="D78">
-        <v>37.53590687393624</v>
+        <v>37.12669626627802</v>
       </c>
       <c r="E78">
-        <v>68.544</v>
+        <v>69.988</v>
       </c>
       <c r="F78">
-        <v>109.744</v>
+        <v>111.188</v>
       </c>
       <c r="G78">
         <v>0.298</v>
@@ -7683,37 +7683,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M78">
-        <v>25.8776352</v>
+        <v>26.2181304</v>
       </c>
       <c r="N78">
-        <v>-15.17430186666667</v>
+        <v>-15.51479706666667</v>
       </c>
       <c r="O78">
-        <v>-2.27614528</v>
+        <v>-2.327219560000001</v>
       </c>
       <c r="P78">
-        <v>-12.89815658666667</v>
+        <v>-13.18757750666667</v>
       </c>
       <c r="Q78">
-        <v>-7.268156586666668</v>
+        <v>-7.557577506666671</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2087202532040431</v>
+        <v>0.2158037424737842</v>
       </c>
       <c r="T78">
-        <v>2.24265860934876</v>
+        <v>2.340165505407402</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06204199060662235</v>
+        <v>0.061236250468874</v>
       </c>
       <c r="W78">
-        <v>0.2211704986149585</v>
+        <v>0.2213604921394395</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4136132707108157</v>
+        <v>0.4082416697924933</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2200824397163388</v>
+        <v>0.2219824397163388</v>
       </c>
       <c r="C79">
-        <v>-73.76330373372198</v>
+        <v>-75.60768826137129</v>
       </c>
       <c r="D79">
-        <v>37.12669626627802</v>
+        <v>36.7263117386287</v>
       </c>
       <c r="E79">
-        <v>69.988</v>
+        <v>71.432</v>
       </c>
       <c r="F79">
-        <v>111.188</v>
+        <v>112.632</v>
       </c>
       <c r="G79">
         <v>0.298</v>
@@ -7765,37 +7765,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M79">
-        <v>26.2181304</v>
+        <v>26.5586256</v>
       </c>
       <c r="N79">
-        <v>-15.51479706666667</v>
+        <v>-15.85529226666667</v>
       </c>
       <c r="O79">
-        <v>-2.327219560000001</v>
+        <v>-2.37829384</v>
       </c>
       <c r="P79">
-        <v>-13.18757750666667</v>
+        <v>-13.47699842666667</v>
       </c>
       <c r="Q79">
-        <v>-7.557577506666671</v>
+        <v>-7.846998426666668</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2158037424737842</v>
+        <v>0.2235311853135016</v>
       </c>
       <c r="T79">
-        <v>2.340165505407402</v>
+        <v>2.446536664744102</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.061236250468874</v>
+        <v>0.06045117033465767</v>
       </c>
       <c r="W79">
-        <v>0.2213604921394395</v>
+        <v>0.2215456140350877</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4082416697924933</v>
+        <v>0.4030078022310511</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2219824397163388</v>
+        <v>0.2238824397163388</v>
       </c>
       <c r="C80">
-        <v>-75.60768826137129</v>
+        <v>-77.44352921107156</v>
       </c>
       <c r="D80">
-        <v>36.7263117386287</v>
+        <v>36.33447078892844</v>
       </c>
       <c r="E80">
-        <v>71.432</v>
+        <v>72.876</v>
       </c>
       <c r="F80">
-        <v>112.632</v>
+        <v>114.076</v>
       </c>
       <c r="G80">
         <v>0.298</v>
@@ -7847,37 +7847,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M80">
-        <v>26.5586256</v>
+        <v>26.8991208</v>
       </c>
       <c r="N80">
-        <v>-15.85529226666667</v>
+        <v>-16.19578746666667</v>
       </c>
       <c r="O80">
-        <v>-2.37829384</v>
+        <v>-2.42936812</v>
       </c>
       <c r="P80">
-        <v>-13.47699842666667</v>
+        <v>-13.76641934666667</v>
       </c>
       <c r="Q80">
-        <v>-7.846998426666668</v>
+        <v>-8.136419346666671</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2235311853135016</v>
+        <v>0.2319945750903351</v>
       </c>
       <c r="T80">
-        <v>2.446536664744102</v>
+        <v>2.563038410684297</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06045117033465767</v>
+        <v>0.0596859656468772</v>
       </c>
       <c r="W80">
-        <v>0.2215456140350877</v>
+        <v>0.2217260493004664</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4030078022310511</v>
+        <v>0.397906437645848</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2238824397163388</v>
+        <v>0.2257824397163388</v>
       </c>
       <c r="C81">
-        <v>-77.44352921107156</v>
+        <v>-79.27109715585422</v>
       </c>
       <c r="D81">
-        <v>36.33447078892844</v>
+        <v>35.95090284414578</v>
       </c>
       <c r="E81">
-        <v>72.876</v>
+        <v>74.32000000000001</v>
       </c>
       <c r="F81">
-        <v>114.076</v>
+        <v>115.52</v>
       </c>
       <c r="G81">
         <v>0.298</v>
@@ -7929,37 +7929,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M81">
-        <v>26.8991208</v>
+        <v>27.23961600000001</v>
       </c>
       <c r="N81">
-        <v>-16.19578746666667</v>
+        <v>-16.53628266666667</v>
       </c>
       <c r="O81">
-        <v>-2.42936812</v>
+        <v>-2.480442400000001</v>
       </c>
       <c r="P81">
-        <v>-13.76641934666667</v>
+        <v>-14.05584026666667</v>
       </c>
       <c r="Q81">
-        <v>-8.136419346666671</v>
+        <v>-8.425840266666672</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2319945750903351</v>
+        <v>0.2413043038448518</v>
       </c>
       <c r="T81">
-        <v>2.563038410684297</v>
+        <v>2.691190331218512</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0596859656468772</v>
+        <v>0.05893989107629122</v>
       </c>
       <c r="W81">
-        <v>0.2217260493004664</v>
+        <v>0.2219019736842105</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.397906437645848</v>
+        <v>0.3929326071752748</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2257824397163388</v>
+        <v>0.2276824397163388</v>
       </c>
       <c r="C82">
-        <v>-79.27109715585422</v>
+        <v>-81.09065136279366</v>
       </c>
       <c r="D82">
-        <v>35.95090284414578</v>
+        <v>35.57534863720635</v>
       </c>
       <c r="E82">
-        <v>74.32000000000001</v>
+        <v>75.76400000000001</v>
       </c>
       <c r="F82">
-        <v>115.52</v>
+        <v>116.964</v>
       </c>
       <c r="G82">
         <v>0.298</v>
@@ -8011,37 +8011,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M82">
-        <v>27.23961600000001</v>
+        <v>27.5801112</v>
       </c>
       <c r="N82">
-        <v>-16.53628266666667</v>
+        <v>-16.87677786666667</v>
       </c>
       <c r="O82">
-        <v>-2.480442400000001</v>
+        <v>-2.531516680000001</v>
       </c>
       <c r="P82">
-        <v>-14.05584026666667</v>
+        <v>-14.34526118666667</v>
       </c>
       <c r="Q82">
-        <v>-8.425840266666672</v>
+        <v>-8.71526118666667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2413043038448518</v>
+        <v>0.2515940040472124</v>
       </c>
       <c r="T82">
-        <v>2.691190331218512</v>
+        <v>2.832831927598434</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05893989107629122</v>
+        <v>0.05821223810004071</v>
       </c>
       <c r="W82">
-        <v>0.2219019736842105</v>
+        <v>0.2220735542560104</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3929326071752748</v>
+        <v>0.3880815873336048</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2276824397163388</v>
+        <v>0.2295824397163388</v>
       </c>
       <c r="C83">
-        <v>-81.09065136279366</v>
+        <v>-82.90244037742977</v>
       </c>
       <c r="D83">
-        <v>35.57534863720635</v>
+        <v>35.20755962257024</v>
       </c>
       <c r="E83">
-        <v>75.76400000000001</v>
+        <v>77.20800000000001</v>
       </c>
       <c r="F83">
-        <v>116.964</v>
+        <v>118.408</v>
       </c>
       <c r="G83">
         <v>0.298</v>
@@ -8093,37 +8093,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M83">
-        <v>27.5801112</v>
+        <v>27.9206064</v>
       </c>
       <c r="N83">
-        <v>-16.87677786666667</v>
+        <v>-17.21727306666667</v>
       </c>
       <c r="O83">
-        <v>-2.531516680000001</v>
+        <v>-2.582590960000001</v>
       </c>
       <c r="P83">
-        <v>-14.34526118666667</v>
+        <v>-14.63468210666667</v>
       </c>
       <c r="Q83">
-        <v>-8.71526118666667</v>
+        <v>-9.004682106666671</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2515940040472124</v>
+        <v>0.2630270042720576</v>
       </c>
       <c r="T83">
-        <v>2.832831927598434</v>
+        <v>2.990211479131681</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05821223810004071</v>
+        <v>0.05750233275735729</v>
       </c>
       <c r="W83">
-        <v>0.2220735542560104</v>
+        <v>0.2222409499358152</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3880815873336048</v>
+        <v>0.3833488850490486</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2295824397163388</v>
+        <v>0.2314824397163388</v>
       </c>
       <c r="C84">
-        <v>-82.90244037742977</v>
+        <v>-84.70670257230979</v>
       </c>
       <c r="D84">
-        <v>35.20755962257024</v>
+        <v>34.84729742769022</v>
       </c>
       <c r="E84">
-        <v>77.20800000000001</v>
+        <v>78.65200000000002</v>
       </c>
       <c r="F84">
-        <v>118.408</v>
+        <v>119.852</v>
       </c>
       <c r="G84">
         <v>0.298</v>
@@ -8175,37 +8175,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M84">
-        <v>27.9206064</v>
+        <v>28.26110160000001</v>
       </c>
       <c r="N84">
-        <v>-17.21727306666667</v>
+        <v>-17.55776826666667</v>
       </c>
       <c r="O84">
-        <v>-2.582590960000001</v>
+        <v>-2.633665240000001</v>
       </c>
       <c r="P84">
-        <v>-14.63468210666667</v>
+        <v>-14.92410302666667</v>
       </c>
       <c r="Q84">
-        <v>-9.004682106666671</v>
+        <v>-9.294103026666672</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2630270042720576</v>
+        <v>0.2758050633468845</v>
       </c>
       <c r="T84">
-        <v>2.990211479131681</v>
+        <v>3.166106272021779</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05750233275735729</v>
+        <v>0.0568095335675096</v>
       </c>
       <c r="W84">
-        <v>0.2222409499358152</v>
+        <v>0.2224043119847812</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3833488850490486</v>
+        <v>0.3787302237833974</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2314824397163388</v>
+        <v>0.2333824397163388</v>
       </c>
       <c r="C85">
-        <v>-84.70670257230979</v>
+        <v>-86.50366666219333</v>
       </c>
       <c r="D85">
-        <v>34.84729742769022</v>
+        <v>34.49433333780669</v>
       </c>
       <c r="E85">
-        <v>78.65200000000002</v>
+        <v>80.09600000000002</v>
       </c>
       <c r="F85">
-        <v>119.852</v>
+        <v>121.296</v>
       </c>
       <c r="G85">
         <v>0.298</v>
@@ -8257,37 +8257,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M85">
-        <v>28.26110160000001</v>
+        <v>28.60159680000001</v>
       </c>
       <c r="N85">
-        <v>-17.55776826666667</v>
+        <v>-17.89826346666667</v>
       </c>
       <c r="O85">
-        <v>-2.633665240000001</v>
+        <v>-2.684739520000001</v>
       </c>
       <c r="P85">
-        <v>-14.92410302666667</v>
+        <v>-15.21352394666667</v>
       </c>
       <c r="Q85">
-        <v>-9.294103026666672</v>
+        <v>-9.583523946666674</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2758050633468845</v>
+        <v>0.2901803798060648</v>
       </c>
       <c r="T85">
-        <v>3.166106272021779</v>
+        <v>3.363987914023141</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0568095335675096</v>
+        <v>0.05613322959646783</v>
       </c>
       <c r="W85">
-        <v>0.2224043119847812</v>
+        <v>0.2225637844611529</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3787302237833974</v>
+        <v>0.3742215306431189</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2333824397163388</v>
+        <v>0.2352824397163388</v>
       </c>
       <c r="C86">
-        <v>-86.50366666219333</v>
+        <v>-88.29355218826076</v>
       </c>
       <c r="D86">
-        <v>34.49433333780669</v>
+        <v>34.14844781173923</v>
       </c>
       <c r="E86">
-        <v>80.096</v>
+        <v>81.53999999999999</v>
       </c>
       <c r="F86">
-        <v>121.296</v>
+        <v>122.74</v>
       </c>
       <c r="G86">
         <v>0.298</v>
@@ -8339,37 +8339,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M86">
-        <v>28.6015968</v>
+        <v>28.942092</v>
       </c>
       <c r="N86">
-        <v>-17.89826346666667</v>
+        <v>-18.23875866666667</v>
       </c>
       <c r="O86">
-        <v>-2.68473952</v>
+        <v>-2.7358138</v>
       </c>
       <c r="P86">
-        <v>-15.21352394666667</v>
+        <v>-15.50294486666667</v>
       </c>
       <c r="Q86">
-        <v>-9.58352394666667</v>
+        <v>-9.872944866666668</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2901803798060646</v>
+        <v>0.3064724051264689</v>
       </c>
       <c r="T86">
-        <v>3.363987914023139</v>
+        <v>3.588253774958015</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05613322959646783</v>
+        <v>0.05547283866003881</v>
       </c>
       <c r="W86">
-        <v>0.2225637844611529</v>
+        <v>0.2227195046439629</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3742215306431189</v>
+        <v>0.3698189244002588</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2352824397163388</v>
+        <v>0.2371824397163388</v>
       </c>
       <c r="C87">
-        <v>-88.29355218826076</v>
+        <v>-90.07656997347905</v>
       </c>
       <c r="D87">
-        <v>34.14844781173923</v>
+        <v>33.80943002652094</v>
       </c>
       <c r="E87">
-        <v>81.53999999999999</v>
+        <v>82.98399999999999</v>
       </c>
       <c r="F87">
-        <v>122.74</v>
+        <v>124.184</v>
       </c>
       <c r="G87">
         <v>0.298</v>
@@ -8421,37 +8421,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M87">
-        <v>28.942092</v>
+        <v>29.2825872</v>
       </c>
       <c r="N87">
-        <v>-18.23875866666667</v>
+        <v>-18.57925386666667</v>
       </c>
       <c r="O87">
-        <v>-2.7358138</v>
+        <v>-2.78688808</v>
       </c>
       <c r="P87">
-        <v>-15.50294486666667</v>
+        <v>-15.79236578666667</v>
       </c>
       <c r="Q87">
-        <v>-9.872944866666668</v>
+        <v>-10.16236578666667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3064724051264689</v>
+        <v>0.3250918626355025</v>
       </c>
       <c r="T87">
-        <v>3.588253774958015</v>
+        <v>3.844557616026445</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05547283866003881</v>
+        <v>0.05482780565236393</v>
       </c>
       <c r="W87">
-        <v>0.2227195046439629</v>
+        <v>0.2228716034271726</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3698189244002588</v>
+        <v>0.3655187043490929</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2371824397163388</v>
+        <v>0.2390824397163388</v>
       </c>
       <c r="C88">
-        <v>-90.07656997347905</v>
+        <v>-91.85292255110932</v>
       </c>
       <c r="D88">
-        <v>33.80943002652094</v>
+        <v>33.47707744889068</v>
       </c>
       <c r="E88">
-        <v>82.98399999999999</v>
+        <v>84.428</v>
       </c>
       <c r="F88">
-        <v>124.184</v>
+        <v>125.628</v>
       </c>
       <c r="G88">
         <v>0.298</v>
@@ -8503,37 +8503,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M88">
-        <v>29.2825872</v>
+        <v>29.6230824</v>
       </c>
       <c r="N88">
-        <v>-18.57925386666667</v>
+        <v>-18.91974906666667</v>
       </c>
       <c r="O88">
-        <v>-2.78688808</v>
+        <v>-2.83796236</v>
       </c>
       <c r="P88">
-        <v>-15.79236578666667</v>
+        <v>-16.08178670666667</v>
       </c>
       <c r="Q88">
-        <v>-10.16236578666667</v>
+        <v>-10.45178670666667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3250918626355025</v>
+        <v>0.3465758520690027</v>
       </c>
       <c r="T88">
-        <v>3.844557616026445</v>
+        <v>4.140292817259248</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05482780565236393</v>
+        <v>0.05419760098969308</v>
       </c>
       <c r="W88">
-        <v>0.2228716034271726</v>
+        <v>0.2230202056866304</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3655187043490929</v>
+        <v>0.3613173399312872</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2390824397163388</v>
+        <v>0.2409824397163388</v>
       </c>
       <c r="C89">
-        <v>-91.85292255110932</v>
+        <v>-93.62280456818695</v>
       </c>
       <c r="D89">
-        <v>33.47707744889068</v>
+        <v>33.15119543181306</v>
       </c>
       <c r="E89">
-        <v>84.428</v>
+        <v>85.872</v>
       </c>
       <c r="F89">
-        <v>125.628</v>
+        <v>127.072</v>
       </c>
       <c r="G89">
         <v>0.298</v>
@@ -8585,37 +8585,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M89">
-        <v>29.6230824</v>
+        <v>29.9635776</v>
       </c>
       <c r="N89">
-        <v>-18.91974906666667</v>
+        <v>-19.26024426666667</v>
       </c>
       <c r="O89">
-        <v>-2.83796236</v>
+        <v>-2.88903664</v>
       </c>
       <c r="P89">
-        <v>-16.08178670666667</v>
+        <v>-16.37120762666667</v>
       </c>
       <c r="Q89">
-        <v>-10.45178670666667</v>
+        <v>-10.74120762666667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3465758520690027</v>
+        <v>0.3716405064080862</v>
       </c>
       <c r="T89">
-        <v>4.140292817259248</v>
+        <v>4.485317218697519</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05419760098969308</v>
+        <v>0.05358171916026475</v>
       </c>
       <c r="W89">
-        <v>0.2230202056866304</v>
+        <v>0.2231654306220096</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3613173399312872</v>
+        <v>0.3572114610684317</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2409824397163388</v>
+        <v>0.2428824397163388</v>
       </c>
       <c r="C90">
-        <v>-93.62280456818695</v>
+        <v>-95.38640316566273</v>
       </c>
       <c r="D90">
-        <v>33.15119543181306</v>
+        <v>32.8315968343373</v>
       </c>
       <c r="E90">
-        <v>85.872</v>
+        <v>87.31600000000002</v>
       </c>
       <c r="F90">
-        <v>127.072</v>
+        <v>128.516</v>
       </c>
       <c r="G90">
         <v>0.298</v>
@@ -8667,37 +8667,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M90">
-        <v>29.9635776</v>
+        <v>30.30407280000001</v>
       </c>
       <c r="N90">
-        <v>-19.26024426666667</v>
+        <v>-19.60073946666667</v>
       </c>
       <c r="O90">
-        <v>-2.88903664</v>
+        <v>-2.940110920000001</v>
       </c>
       <c r="P90">
-        <v>-16.37120762666667</v>
+        <v>-16.66062854666667</v>
       </c>
       <c r="Q90">
-        <v>-10.74120762666667</v>
+        <v>-11.03062854666667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3716405064080862</v>
+        <v>0.4012623706270032</v>
       </c>
       <c r="T90">
-        <v>4.485317218697519</v>
+        <v>4.893073329488203</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05358171916026475</v>
+        <v>0.05297967737194716</v>
       </c>
       <c r="W90">
-        <v>0.2231654306220096</v>
+        <v>0.2233073920756949</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3572114610684317</v>
+        <v>0.3531978491463145</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2428824397163388</v>
+        <v>0.2447824397163388</v>
       </c>
       <c r="C91">
-        <v>-95.38640316566273</v>
+        <v>-97.14389833676509</v>
       </c>
       <c r="D91">
-        <v>32.8315968343373</v>
+        <v>32.51810166323492</v>
       </c>
       <c r="E91">
-        <v>87.31600000000002</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="F91">
-        <v>128.516</v>
+        <v>129.96</v>
       </c>
       <c r="G91">
         <v>0.298</v>
@@ -8749,37 +8749,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M91">
-        <v>30.30407280000001</v>
+        <v>30.644568</v>
       </c>
       <c r="N91">
-        <v>-19.60073946666667</v>
+        <v>-19.94123466666667</v>
       </c>
       <c r="O91">
-        <v>-2.940110920000001</v>
+        <v>-2.9911852</v>
       </c>
       <c r="P91">
-        <v>-16.66062854666667</v>
+        <v>-16.95004946666667</v>
       </c>
       <c r="Q91">
-        <v>-11.03062854666667</v>
+        <v>-11.32004946666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4012623706270032</v>
+        <v>0.4368086076897035</v>
       </c>
       <c r="T91">
-        <v>4.893073329488203</v>
+        <v>5.382380662437024</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05297967737194716</v>
+        <v>0.05239101429003665</v>
       </c>
       <c r="W91">
-        <v>0.2233073920756949</v>
+        <v>0.2234461988304094</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3531978491463145</v>
+        <v>0.3492734286002444</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2447824397163388</v>
+        <v>0.2466824397163388</v>
       </c>
       <c r="C92">
-        <v>-97.14389833676509</v>
+        <v>-98.89546326502557</v>
       </c>
       <c r="D92">
-        <v>32.51810166323492</v>
+        <v>32.21053673497443</v>
       </c>
       <c r="E92">
-        <v>88.76000000000001</v>
+        <v>90.20399999999999</v>
       </c>
       <c r="F92">
-        <v>129.96</v>
+        <v>131.404</v>
       </c>
       <c r="G92">
         <v>0.298</v>
@@ -8831,37 +8831,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M92">
-        <v>30.644568</v>
+        <v>30.9850632</v>
       </c>
       <c r="N92">
-        <v>-19.94123466666667</v>
+        <v>-20.28172986666667</v>
       </c>
       <c r="O92">
-        <v>-2.9911852</v>
+        <v>-3.04225948</v>
       </c>
       <c r="P92">
-        <v>-16.95004946666667</v>
+        <v>-17.23947038666667</v>
       </c>
       <c r="Q92">
-        <v>-11.32004946666667</v>
+        <v>-11.60947038666667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4368086076897035</v>
+        <v>0.4802540085441152</v>
       </c>
       <c r="T92">
-        <v>5.382380662437024</v>
+        <v>5.980422958263361</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05239101429003665</v>
+        <v>0.05181528885827801</v>
       </c>
       <c r="W92">
-        <v>0.2234461988304094</v>
+        <v>0.223581954887218</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3492734286002444</v>
+        <v>0.3454352590551868</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2466824397163388</v>
+        <v>0.2485824397163388</v>
       </c>
       <c r="C93">
-        <v>-98.89546326502557</v>
+        <v>-100.641264643301</v>
       </c>
       <c r="D93">
-        <v>32.21053673497443</v>
+        <v>31.90873535669898</v>
       </c>
       <c r="E93">
-        <v>90.20399999999999</v>
+        <v>91.64800000000001</v>
       </c>
       <c r="F93">
-        <v>131.404</v>
+        <v>132.848</v>
       </c>
       <c r="G93">
         <v>0.298</v>
@@ -8913,37 +8913,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M93">
-        <v>30.9850632</v>
+        <v>31.32555840000001</v>
       </c>
       <c r="N93">
-        <v>-20.28172986666667</v>
+        <v>-20.62222506666667</v>
       </c>
       <c r="O93">
-        <v>-3.04225948</v>
+        <v>-3.093333760000001</v>
       </c>
       <c r="P93">
-        <v>-17.23947038666667</v>
+        <v>-17.52889130666667</v>
       </c>
       <c r="Q93">
-        <v>-11.60947038666667</v>
+        <v>-11.89889130666667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4802540085441152</v>
+        <v>0.5345607596121297</v>
       </c>
       <c r="T93">
-        <v>5.980422958263361</v>
+        <v>6.727975828046283</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05181528885827801</v>
+        <v>0.05125207919677498</v>
       </c>
       <c r="W93">
-        <v>0.223581954887218</v>
+        <v>0.2237147597254005</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3454352590551868</v>
+        <v>0.3416805279784999</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2485824397163388</v>
+        <v>0.2504824397163388</v>
       </c>
       <c r="C94">
-        <v>-100.641264643301</v>
+        <v>-102.3814629750277</v>
       </c>
       <c r="D94">
-        <v>31.90873535669898</v>
+        <v>31.6125370249723</v>
       </c>
       <c r="E94">
-        <v>91.64800000000001</v>
+        <v>93.092</v>
       </c>
       <c r="F94">
-        <v>132.848</v>
+        <v>134.292</v>
       </c>
       <c r="G94">
         <v>0.298</v>
@@ -8995,37 +8995,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M94">
-        <v>31.32555840000001</v>
+        <v>31.6660536</v>
       </c>
       <c r="N94">
-        <v>-20.62222506666667</v>
+        <v>-20.96272026666667</v>
       </c>
       <c r="O94">
-        <v>-3.093333760000001</v>
+        <v>-3.14440804</v>
       </c>
       <c r="P94">
-        <v>-17.52889130666667</v>
+        <v>-17.81831222666667</v>
       </c>
       <c r="Q94">
-        <v>-11.89889130666667</v>
+        <v>-12.18831222666667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5345607596121297</v>
+        <v>0.6043837252710053</v>
       </c>
       <c r="T94">
-        <v>6.727975828046283</v>
+        <v>7.689115232052895</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05125207919677498</v>
+        <v>0.05070098157100322</v>
       </c>
       <c r="W94">
-        <v>0.2237147597254005</v>
+        <v>0.2238447085455574</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3416805279784999</v>
+        <v>0.338006543806688</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2504824397163388</v>
+        <v>0.2523824397163388</v>
       </c>
       <c r="C95">
-        <v>-102.3814629750277</v>
+        <v>-104.116212858851</v>
       </c>
       <c r="D95">
-        <v>31.6125370249723</v>
+        <v>31.32178714114905</v>
       </c>
       <c r="E95">
-        <v>93.092</v>
+        <v>94.53600000000002</v>
       </c>
       <c r="F95">
-        <v>134.292</v>
+        <v>135.736</v>
       </c>
       <c r="G95">
         <v>0.298</v>
@@ -9077,37 +9077,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M95">
-        <v>31.6660536</v>
+        <v>32.0065488</v>
       </c>
       <c r="N95">
-        <v>-20.96272026666667</v>
+        <v>-21.30321546666667</v>
       </c>
       <c r="O95">
-        <v>-3.14440804</v>
+        <v>-3.19548232</v>
       </c>
       <c r="P95">
-        <v>-17.81831222666667</v>
+        <v>-18.10773314666667</v>
       </c>
       <c r="Q95">
-        <v>-12.18831222666667</v>
+        <v>-12.47773314666667</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6043837252710053</v>
+        <v>0.697481012816173</v>
       </c>
       <c r="T95">
-        <v>7.689115232052895</v>
+        <v>8.970634437395047</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05070098157100322</v>
+        <v>0.05016160942663083</v>
       </c>
       <c r="W95">
-        <v>0.2238447085455574</v>
+        <v>0.2239718924972005</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.338006543806688</v>
+        <v>0.3344107295108723</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2523824397163388</v>
+        <v>0.2542824397163388</v>
       </c>
       <c r="C96">
-        <v>-104.116212858851</v>
+        <v>-105.845663257691</v>
       </c>
       <c r="D96">
-        <v>31.32178714114905</v>
+        <v>31.03633674230896</v>
       </c>
       <c r="E96">
-        <v>94.53600000000002</v>
+        <v>95.98</v>
       </c>
       <c r="F96">
-        <v>135.736</v>
+        <v>137.18</v>
       </c>
       <c r="G96">
         <v>0.298</v>
@@ -9159,37 +9159,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M96">
-        <v>32.0065488</v>
+        <v>32.347044</v>
       </c>
       <c r="N96">
-        <v>-21.30321546666667</v>
+        <v>-21.64371066666667</v>
       </c>
       <c r="O96">
-        <v>-3.19548232</v>
+        <v>-3.2465566</v>
       </c>
       <c r="P96">
-        <v>-18.10773314666667</v>
+        <v>-18.39715406666667</v>
       </c>
       <c r="Q96">
-        <v>-12.47773314666667</v>
+        <v>-12.76715406666667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.697481012816173</v>
+        <v>0.8278172153794081</v>
       </c>
       <c r="T96">
-        <v>8.970634437395047</v>
+        <v>10.76476132487406</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05016160942663083</v>
+        <v>0.04963359248529788</v>
       </c>
       <c r="W96">
-        <v>0.2239718924972005</v>
+        <v>0.2240963988919668</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3344107295108723</v>
+        <v>0.3308906165686525</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2542824397163388</v>
+        <v>0.2561824397163388</v>
       </c>
       <c r="C97">
-        <v>-105.845663257691</v>
+        <v>-107.5699577532293</v>
       </c>
       <c r="D97">
-        <v>31.03633674230896</v>
+        <v>30.75604224677075</v>
       </c>
       <c r="E97">
-        <v>95.98</v>
+        <v>97.42400000000002</v>
       </c>
       <c r="F97">
-        <v>137.18</v>
+        <v>138.624</v>
       </c>
       <c r="G97">
         <v>0.298</v>
@@ -9241,37 +9241,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M97">
-        <v>32.347044</v>
+        <v>32.68753920000001</v>
       </c>
       <c r="N97">
-        <v>-21.64371066666667</v>
+        <v>-21.98420586666668</v>
       </c>
       <c r="O97">
-        <v>-3.2465566</v>
+        <v>-3.297630880000002</v>
       </c>
       <c r="P97">
-        <v>-18.39715406666667</v>
+        <v>-18.68657498666668</v>
       </c>
       <c r="Q97">
-        <v>-12.76715406666667</v>
+        <v>-13.05657498666668</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8278172153794081</v>
+        <v>1.023321519224261</v>
       </c>
       <c r="T97">
-        <v>10.76476132487406</v>
+        <v>13.45595165609258</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04963359248529788</v>
+        <v>0.04911657589690934</v>
       </c>
       <c r="W97">
-        <v>0.2240963988919668</v>
+        <v>0.2242183114035088</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3308906165686525</v>
+        <v>0.327443839312729</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2561824397163388</v>
+        <v>0.2580824397163388</v>
       </c>
       <c r="C98">
-        <v>-107.5699577532292</v>
+        <v>-109.2892347867274</v>
       </c>
       <c r="D98">
-        <v>30.75604224677075</v>
+        <v>30.48076521327261</v>
       </c>
       <c r="E98">
-        <v>97.42399999999999</v>
+        <v>98.86800000000001</v>
       </c>
       <c r="F98">
-        <v>138.624</v>
+        <v>140.068</v>
       </c>
       <c r="G98">
         <v>0.298</v>
@@ -9323,37 +9323,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M98">
-        <v>32.6875392</v>
+        <v>33.0280344</v>
       </c>
       <c r="N98">
-        <v>-21.98420586666667</v>
+        <v>-22.32470106666667</v>
       </c>
       <c r="O98">
-        <v>-3.29763088</v>
+        <v>-3.34870516</v>
       </c>
       <c r="P98">
-        <v>-18.68657498666667</v>
+        <v>-18.97599590666667</v>
       </c>
       <c r="Q98">
-        <v>-13.05657498666667</v>
+        <v>-13.34599590666667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.023321519224258</v>
+        <v>1.349162025632344</v>
       </c>
       <c r="T98">
-        <v>13.45595165609255</v>
+        <v>17.94126887479007</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04911657589690936</v>
+        <v>0.0486102194443639</v>
       </c>
       <c r="W98">
-        <v>0.2242183114035088</v>
+        <v>0.224337710255019</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.327443839312729</v>
+        <v>0.3240681296290927</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2580824397163388</v>
+        <v>0.2599824397163387</v>
       </c>
       <c r="C99">
-        <v>-109.2892347867274</v>
+        <v>-111.0036278870297</v>
       </c>
       <c r="D99">
-        <v>30.48076521327261</v>
+        <v>30.21037211297029</v>
       </c>
       <c r="E99">
-        <v>98.86800000000001</v>
+        <v>100.312</v>
       </c>
       <c r="F99">
-        <v>140.068</v>
+        <v>141.512</v>
       </c>
       <c r="G99">
         <v>0.298</v>
@@ -9405,37 +9405,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M99">
-        <v>33.0280344</v>
+        <v>33.3685296</v>
       </c>
       <c r="N99">
-        <v>-22.32470106666667</v>
+        <v>-22.66519626666667</v>
       </c>
       <c r="O99">
-        <v>-3.34870516</v>
+        <v>-3.39977944</v>
       </c>
       <c r="P99">
-        <v>-18.97599590666667</v>
+        <v>-19.26541682666667</v>
       </c>
       <c r="Q99">
-        <v>-13.34599590666667</v>
+        <v>-13.63541682666667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.349162025632344</v>
+        <v>2.000843038448516</v>
       </c>
       <c r="T99">
-        <v>17.94126887479007</v>
+        <v>26.91190331218509</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0486102194443639</v>
+        <v>0.04811419679697243</v>
       </c>
       <c r="W99">
-        <v>0.224337710255019</v>
+        <v>0.2244546723952739</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3240681296290927</v>
+        <v>0.3207613119798163</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2599824397163387</v>
+        <v>0.2618824397163388</v>
       </c>
       <c r="C100">
-        <v>-111.0036278870297</v>
+        <v>-112.7132658865358</v>
       </c>
       <c r="D100">
-        <v>30.21037211297029</v>
+        <v>29.94473411346418</v>
       </c>
       <c r="E100">
-        <v>100.312</v>
+        <v>101.756</v>
       </c>
       <c r="F100">
-        <v>141.512</v>
+        <v>142.956</v>
       </c>
       <c r="G100">
         <v>0.298</v>
@@ -9487,37 +9487,37 @@
         <v>10.70333333333333</v>
       </c>
       <c r="M100">
-        <v>33.3685296</v>
+        <v>33.70902480000001</v>
       </c>
       <c r="N100">
-        <v>-22.66519626666667</v>
+        <v>-23.00569146666668</v>
       </c>
       <c r="O100">
-        <v>-3.39977944</v>
+        <v>-3.450853720000001</v>
       </c>
       <c r="P100">
-        <v>-19.26541682666667</v>
+        <v>-19.55483774666667</v>
       </c>
       <c r="Q100">
-        <v>-13.63541682666667</v>
+        <v>-13.92483774666668</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.000843038448516</v>
+        <v>3.955886076897031</v>
       </c>
       <c r="T100">
-        <v>26.91190331218509</v>
+        <v>53.82380662437019</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04811419679697243</v>
+        <v>0.04762819480912422</v>
       </c>
       <c r="W100">
-        <v>0.2244546723952739</v>
+        <v>0.2245692716640085</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3207613119798163</v>
+        <v>0.3175212987274948</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2618824397163388</v>
-      </c>
-      <c r="C101">
-        <v>-112.7132658865358</v>
-      </c>
-      <c r="D101">
-        <v>29.94473411346418</v>
-      </c>
-      <c r="E101">
-        <v>101.756</v>
-      </c>
-      <c r="F101">
-        <v>142.956</v>
-      </c>
-      <c r="G101">
-        <v>0.298</v>
-      </c>
-      <c r="H101">
-        <v>103.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>16.33333333333333</v>
-      </c>
-      <c r="K101">
-        <v>5.63</v>
-      </c>
-      <c r="L101">
-        <v>10.70333333333333</v>
-      </c>
-      <c r="M101">
-        <v>33.70902480000001</v>
-      </c>
-      <c r="N101">
-        <v>-23.00569146666668</v>
-      </c>
-      <c r="O101">
-        <v>-3.450853720000001</v>
-      </c>
-      <c r="P101">
-        <v>-19.55483774666667</v>
-      </c>
-      <c r="Q101">
-        <v>-13.92483774666668</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.955886076897031</v>
-      </c>
-      <c r="T101">
-        <v>53.82380662437019</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04762819480912422</v>
-      </c>
-      <c r="W101">
-        <v>0.2245692716640085</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3175212987274948</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
